--- a/Lots_Musique_250_RM45-60.xlsx
+++ b/Lots_Musique_250_RM45-60.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4031" uniqueCount="1442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4103" uniqueCount="1476">
   <si>
     <t xml:space="preserve">Lots musique – 250 lots entre RM45 et RM60</t>
   </si>
@@ -2514,6 +2514,51 @@
     <t xml:space="preserve">Cassette - Jack White "Frozen Charlotte" (7th studio album, rock)</t>
   </si>
   <si>
+    <t xml:space="preserve">Johnny Cash Music Boxy Graphic Tee (Cotton On, licensed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://cottonon.com/MY/johnny-cash-music-boxy-graphic-tee/2059306-79.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cotton On Malaysia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ships within Malaysia (cottonon.com/MY)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product page price 45.00 (sale from RM109); size selector: XS, 2XS, 3XS available, S/M out of stock - checked 2026-10-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-shirt officiel (licensed artist merch) - Johnny Cash; women's boxy fit, only small sizes left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K-Pop Demon Hunters 4 Inch Mini Figure - Assorted (1 pc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.toysrus.com.my/k-pop-demon-hunter-4-inch-mini-figure---assorted-1pc-10163048.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toys"R"Us Malaysia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ships within Malaysia (toysrus.com.my)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product page schema.org availability=InStock + 'Add to Cart' shown, price verified - checked 2026-10-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figurine - KPop Demon Hunters (K-pop idol film/soundtrack, 'Golden'); random character</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAKI Rose Plante Music Box (building-block music box)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.toysrus.com.my/jaki-rose-plante-music-box-10042193.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boite a musique - buildable brick music box (plays a melody when wound), no instrument needed</t>
+  </si>
+  <si>
     <t xml:space="preserve">Beyonce Knowles Pop Art (10'X10')</t>
   </si>
   <si>
@@ -2539,33 +2584,6 @@
   </si>
   <si>
     <t xml:space="preserve">Pin's collector - Snoopy records-themed enamel pin (Peanuts licensed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bob Dylan Pop Art (10'X10')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.bookxcess.com/products/bob-dylan-pop-art-10x10-286760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cadre pop-art musicien (framed 26x26cm glossy pop-art print, ready to hang) - Bob Dylan. Same product line as other pop-art prints.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aespa FANLIGHT EMBLEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://xduniverse.com.my/products/aespa-fanlight-emblem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merch K-pop officiel - Embleme de lightstick officiel; artist: AESPA; in-stock variants: KARINA, WINTER; sold by XD Universe as 'Ship from Malaysia, ready stock'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vinyl Styl Audio Cassette Head Cleaner &amp; Demagnetizer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.sweelee.com.my/products/vinyl-styl-audio-cassette-head-cleaner-and-demagnetizer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kit nettoyage cassette - tape head cleaner &amp; demagnetizer</t>
   </si>
   <si>
     <t xml:space="preserve">Neil Diamond – Jonathan Livingston Seagull OST (LP, gatefold)</t>
@@ -4097,6 +4115,33 @@
     <t xml:space="preserve">Britney Spears memoir (bestseller); text-led with photo inserts - lower priority for 'beautiful pictures'</t>
   </si>
   <si>
+    <t xml:space="preserve">Bob Dylan Pop Art (10'X10')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bookxcess.com/products/bob-dylan-pop-art-10x10-286760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cadre pop-art musicien (framed 26x26cm glossy pop-art print, ready to hang) - Bob Dylan. Same product line as other pop-art prints.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aespa FANLIGHT EMBLEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://xduniverse.com.my/products/aespa-fanlight-emblem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merch K-pop officiel - Embleme de lightstick officiel; artist: AESPA; in-stock variants: KARINA, WINTER; sold by XD Universe as 'Ship from Malaysia, ready stock'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vinyl Styl Audio Cassette Head Cleaner &amp; Demagnetizer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.sweelee.com.my/products/vinyl-styl-audio-cassette-head-cleaner-and-demagnetizer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kit nettoyage cassette - tape head cleaner &amp; demagnetizer</t>
+  </si>
+  <si>
     <t xml:space="preserve">Frank Sinatra Pop Art (10X10)</t>
   </si>
   <si>
@@ -4277,6 +4322,18 @@
     <t xml:space="preserve">Cadre pop-art musicien (framed 26x26cm glossy pop-art print, ready to hang) - Yoshiki (X Japan). Same product line as other pop-art prints.</t>
   </si>
   <si>
+    <t xml:space="preserve">Lisa (BLACKPINK) Music Boxy Graphic Tee (Cotton On, licensed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://cottonon.com/MY/lisa-music-boxy-graphic-tee/2059306-158.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product page price 60.00 (sale from RM129); sizes 3XS, 2XS, XS, S, XL available (M, L out of stock) - checked 2026-10-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-shirt officiel (licensed artist merch) - LISA of BLACKPINK; women's boxy fit</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fender Amp Logo Patch</t>
   </si>
   <si>
@@ -4395,6 +4452,51 @@
   </si>
   <si>
     <t xml:space="preserve">Cassette - Indonesian folk duo (SE Asian band), 1 unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAKI Pink Rose Music Box (building-block music box)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.toysrus.com.my/jaki-pink-rose-music-box-10042194.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boite a musique - buildable brick music box, pink rose design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPop Demon Hunters Acrylic Board - Huntr/X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.toysrus.com.my/kpop-demon-hunters-acrylic-board---huntr-x-10131256.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acrylic board collectible - Huntr/X (the K-pop girl group of KPop Demon Hunters)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPop Demon Hunters Acrylic Standee - Huntr/X Rumi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.toysrus.com.my/kpop-demon-hunters-acrylic-standee---huntr-x-rumi-10131252.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acrylic standee collectible - K-pop idol theme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPop Demon Hunters Flat Plush Keychain - Huntrix Rumi (Golden Version)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.toysrus.com.my/kpop-demon-hunters-flat-plush-keychain---huntrix-rumi-golden-version-10131258.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porte-cles peluche - 'Golden' song version, K-pop theme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPop Demon Hunters Flat Plush Keychain - Saja Boys Jinu (Soda Pop Version)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.toysrus.com.my/kpop-demon-hunters-flat-plush-keychain---saja-boys-jinu-soda-pop-version-10131261.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porte-cles peluche - Saja Boys boy band, 'Soda Pop' song version</t>
   </si>
   <si>
     <t xml:space="preserve">2026 G-DRAGON 'FAM' MEETING [FAM+ILY : FAMILY: FAM I LOVE YOU] OFFICIAL MD - PHOTOCARD PACK</t>
@@ -5140,8 +5242,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Reserve" displayName="Reserve" ref="A1:J249" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:J249"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Reserve" displayName="Reserve" ref="A1:J258" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:J258"/>
   <tableColumns count="10">
     <tableColumn id="1" name="N°"/>
     <tableColumn id="2" name="Catégorie"/>
@@ -5405,7 +5507,7 @@
         <v>4608</v>
       </c>
       <c r="G5" s="4" t="n">
-        <f aca="false">COUNTIF(Réserve!$B$2:$B$249,A5)</f>
+        <f aca="false">COUNTIF(Réserve!$B$2:$B$258,A5)</f>
         <v>151</v>
       </c>
     </row>
@@ -5433,7 +5535,7 @@
         <v>3192</v>
       </c>
       <c r="G6" s="4" t="n">
-        <f aca="false">COUNTIF(Réserve!$B$2:$B$249,A6)</f>
+        <f aca="false">COUNTIF(Réserve!$B$2:$B$258,A6)</f>
         <v>14</v>
       </c>
     </row>
@@ -5461,7 +5563,7 @@
         <v>3812.58</v>
       </c>
       <c r="G7" s="4" t="n">
-        <f aca="false">COUNTIF(Réserve!$B$2:$B$249,A7)</f>
+        <f aca="false">COUNTIF(Réserve!$B$2:$B$258,A7)</f>
         <v>13</v>
       </c>
     </row>
@@ -5489,7 +5591,7 @@
         <v>658.7</v>
       </c>
       <c r="G8" s="4" t="n">
-        <f aca="false">COUNTIF(Réserve!$B$2:$B$249,A8)</f>
+        <f aca="false">COUNTIF(Réserve!$B$2:$B$258,A8)</f>
         <v>17</v>
       </c>
     </row>
@@ -5510,15 +5612,15 @@
       </c>
       <c r="E9" s="7" t="n">
         <f aca="false">IFERROR(AVERAGEIF(Lots!$B$2:$B$251,A9,Lots!$D$2:$D$251),0)</f>
-        <v>57.6416666666667</v>
+        <v>56.4</v>
       </c>
       <c r="F9" s="7" t="n">
         <f aca="false">SUMIF(Lots!$B$2:$B$251,A9,Lots!$D$2:$D$251)</f>
-        <v>691.7</v>
+        <v>676.8</v>
       </c>
       <c r="G9" s="4" t="n">
-        <f aca="false">COUNTIF(Réserve!$B$2:$B$249,A9)</f>
-        <v>53</v>
+        <f aca="false">COUNTIF(Réserve!$B$2:$B$258,A9)</f>
+        <v>62</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5536,15 +5638,15 @@
       </c>
       <c r="E10" s="11" t="n">
         <f aca="false">IFERROR(AVERAGE(Lots!$D$2:$D$251),0)</f>
-        <v>51.85192</v>
+        <v>51.79232</v>
       </c>
       <c r="F10" s="11" t="n">
         <f aca="false">SUM(F5:F9)</f>
-        <v>12962.98</v>
+        <v>12948.08</v>
       </c>
       <c r="G10" s="8" t="n">
         <f aca="false">SUM(G5:G9)</f>
-        <v>248</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13475,7 +13577,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="246" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="16" t="n">
         <v>245</v>
       </c>
@@ -13486,25 +13588,25 @@
         <v>791</v>
       </c>
       <c r="D246" s="19" t="n">
-        <v>59.9</v>
+        <v>45</v>
       </c>
       <c r="E246" s="20" t="s">
         <v>792</v>
       </c>
       <c r="F246" s="16" t="s">
-        <v>726</v>
+        <v>793</v>
       </c>
       <c r="G246" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H246" s="18" t="s">
-        <v>768</v>
+        <v>794</v>
       </c>
       <c r="I246" s="18" t="s">
-        <v>728</v>
+        <v>795</v>
       </c>
       <c r="J246" s="18" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13515,28 +13617,28 @@
         <v>14</v>
       </c>
       <c r="C247" s="18" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="D247" s="19" t="n">
-        <v>55</v>
+        <v>59.5</v>
       </c>
       <c r="E247" s="20" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="F247" s="16" t="s">
-        <v>772</v>
+        <v>799</v>
       </c>
       <c r="G247" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H247" s="18" t="s">
-        <v>773</v>
+        <v>800</v>
       </c>
       <c r="I247" s="18" t="s">
-        <v>774</v>
+        <v>801</v>
       </c>
       <c r="J247" s="18" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13547,28 +13649,28 @@
         <v>14</v>
       </c>
       <c r="C248" s="18" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="D248" s="19" t="n">
-        <v>60</v>
+        <v>48.5</v>
       </c>
       <c r="E248" s="20" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="F248" s="16" t="s">
-        <v>772</v>
+        <v>799</v>
       </c>
       <c r="G248" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H248" s="18" t="s">
-        <v>773</v>
+        <v>800</v>
       </c>
       <c r="I248" s="18" t="s">
-        <v>774</v>
+        <v>801</v>
       </c>
       <c r="J248" s="18" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13579,13 +13681,13 @@
         <v>14</v>
       </c>
       <c r="C249" s="18" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="D249" s="19" t="n">
         <v>59.9</v>
       </c>
       <c r="E249" s="20" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="F249" s="16" t="s">
         <v>726</v>
@@ -13600,10 +13702,10 @@
         <v>728</v>
       </c>
       <c r="J249" s="18" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="250" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="16" t="n">
         <v>249</v>
       </c>
@@ -13611,28 +13713,28 @@
         <v>14</v>
       </c>
       <c r="C250" s="18" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="D250" s="19" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E250" s="20" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="F250" s="16" t="s">
-        <v>784</v>
+        <v>772</v>
       </c>
       <c r="G250" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H250" s="18" t="s">
-        <v>785</v>
+        <v>773</v>
       </c>
       <c r="I250" s="18" t="s">
-        <v>786</v>
+        <v>774</v>
       </c>
       <c r="J250" s="18" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13643,13 +13745,13 @@
         <v>14</v>
       </c>
       <c r="C251" s="18" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="D251" s="19" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E251" s="20" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="F251" s="16" t="s">
         <v>772</v>
@@ -13664,7 +13766,7 @@
         <v>774</v>
       </c>
       <c r="J251" s="18" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
     </row>
   </sheetData>
@@ -13913,12 +14015,12 @@
     <hyperlink ref="E243" r:id="rId242" display="https://www.sweelee.com.my/products/pintrill-snoopy-headphones-records-pin"/>
     <hyperlink ref="E244" r:id="rId243" display="https://xduniverse.com.my/products/bornpink-blackpink-polaroid-photo-sticker-set"/>
     <hyperlink ref="E245" r:id="rId244" display="https://www.sweelee.com.my/products/frozen-charlotte-jack-white-cassette-sd"/>
-    <hyperlink ref="E246" r:id="rId245" display="https://www.bookxcess.com/products/beyonce-knowles-pop-art-10x10-286831"/>
-    <hyperlink ref="E247" r:id="rId246" display="https://www.sweelee.com.my/products/behringer-hpm1000-all-purpose-closed-back-headphones"/>
-    <hyperlink ref="E248" r:id="rId247" display="https://www.sweelee.com.my/products/pintrill-snoopy-blue-cap-records-pin"/>
-    <hyperlink ref="E249" r:id="rId248" display="https://www.bookxcess.com/products/bob-dylan-pop-art-10x10-286760"/>
-    <hyperlink ref="E250" r:id="rId249" display="https://xduniverse.com.my/products/aespa-fanlight-emblem"/>
-    <hyperlink ref="E251" r:id="rId250" display="https://www.sweelee.com.my/products/vinyl-styl-audio-cassette-head-cleaner-and-demagnetizer"/>
+    <hyperlink ref="E246" r:id="rId245" display="https://cottonon.com/MY/johnny-cash-music-boxy-graphic-tee/2059306-79.html"/>
+    <hyperlink ref="E247" r:id="rId246" display="https://www.toysrus.com.my/k-pop-demon-hunter-4-inch-mini-figure---assorted-1pc-10163048.html"/>
+    <hyperlink ref="E248" r:id="rId247" display="https://www.toysrus.com.my/jaki-rose-plante-music-box-10042193.html"/>
+    <hyperlink ref="E249" r:id="rId248" display="https://www.bookxcess.com/products/beyonce-knowles-pop-art-10x10-286831"/>
+    <hyperlink ref="E250" r:id="rId249" display="https://www.sweelee.com.my/products/behringer-hpm1000-all-purpose-closed-back-headphones"/>
+    <hyperlink ref="E251" r:id="rId250" display="https://www.sweelee.com.my/products/pintrill-snoopy-blue-cap-records-pin"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -13938,7 +14040,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J249"/>
+  <dimension ref="A1:J258"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -13992,13 +14094,13 @@
         <v>9</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="D2" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="F2" s="16" t="s">
         <v>197</v>
@@ -14024,13 +14126,13 @@
         <v>9</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="D3" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="F3" s="16" t="s">
         <v>197</v>
@@ -14056,13 +14158,13 @@
         <v>9</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="D4" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="F4" s="16" t="s">
         <v>197</v>
@@ -14088,13 +14190,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="D5" s="19" t="n">
         <v>53</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="F5" s="16" t="s">
         <v>197</v>
@@ -14120,13 +14222,13 @@
         <v>9</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="D6" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="F6" s="16" t="s">
         <v>197</v>
@@ -14152,13 +14254,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="D7" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>197</v>
@@ -14184,13 +14286,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="D8" s="19" t="n">
         <v>49</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>197</v>
@@ -14216,13 +14318,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="D9" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="F9" s="16" t="s">
         <v>197</v>
@@ -14248,13 +14350,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="D10" s="19" t="n">
         <v>49</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="F10" s="16" t="s">
         <v>197</v>
@@ -14280,13 +14382,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="D11" s="19" t="n">
         <v>56</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="F11" s="16" t="s">
         <v>197</v>
@@ -14312,13 +14414,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="D12" s="19" t="n">
         <v>56</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>197</v>
@@ -14344,13 +14446,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="D13" s="19" t="n">
         <v>53</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="F13" s="16" t="s">
         <v>197</v>
@@ -14376,13 +14478,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="D14" s="19" t="n">
         <v>56</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="F14" s="16" t="s">
         <v>197</v>
@@ -14408,13 +14510,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="D15" s="19" t="n">
         <v>49</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="F15" s="16" t="s">
         <v>197</v>
@@ -14440,13 +14542,13 @@
         <v>9</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="D16" s="19" t="n">
         <v>56</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="F16" s="16" t="s">
         <v>197</v>
@@ -14472,13 +14574,13 @@
         <v>9</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="D17" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="F17" s="16" t="s">
         <v>197</v>
@@ -14504,13 +14606,13 @@
         <v>9</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="D18" s="19" t="n">
         <v>56</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="F18" s="16" t="s">
         <v>197</v>
@@ -14536,13 +14638,13 @@
         <v>9</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="D19" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="F19" s="16" t="s">
         <v>197</v>
@@ -14568,13 +14670,13 @@
         <v>9</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="D20" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="F20" s="16" t="s">
         <v>197</v>
@@ -14600,13 +14702,13 @@
         <v>9</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="D21" s="19" t="n">
         <v>49</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="F21" s="16" t="s">
         <v>197</v>
@@ -14632,13 +14734,13 @@
         <v>9</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="D22" s="19" t="n">
         <v>49</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="F22" s="16" t="s">
         <v>197</v>
@@ -14664,13 +14766,13 @@
         <v>9</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="D23" s="19" t="n">
         <v>56</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="F23" s="16" t="s">
         <v>197</v>
@@ -14696,13 +14798,13 @@
         <v>9</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="D24" s="19" t="n">
         <v>57</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="F24" s="16" t="s">
         <v>197</v>
@@ -14717,7 +14819,7 @@
         <v>200</v>
       </c>
       <c r="J24" s="18" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14728,13 +14830,13 @@
         <v>9</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="D25" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="F25" s="16" t="s">
         <v>197</v>
@@ -14760,13 +14862,13 @@
         <v>9</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="D26" s="19" t="n">
         <v>56</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="F26" s="16" t="s">
         <v>197</v>
@@ -14792,13 +14894,13 @@
         <v>9</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="D27" s="19" t="n">
         <v>59</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="F27" s="16" t="s">
         <v>37</v>
@@ -14824,13 +14926,13 @@
         <v>9</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="D28" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="F28" s="16" t="s">
         <v>37</v>
@@ -14856,13 +14958,13 @@
         <v>9</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="D29" s="19" t="n">
         <v>59</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="F29" s="16" t="s">
         <v>37</v>
@@ -14874,7 +14976,7 @@
         <v>39</v>
       </c>
       <c r="I29" s="18" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="J29" s="18" t="s">
         <v>58</v>
@@ -14888,13 +14990,13 @@
         <v>9</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="D30" s="19" t="n">
         <v>49</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="F30" s="16" t="s">
         <v>37</v>
@@ -14920,13 +15022,13 @@
         <v>9</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="D31" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="F31" s="16" t="s">
         <v>37</v>
@@ -14952,13 +15054,13 @@
         <v>9</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="D32" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="F32" s="16" t="s">
         <v>37</v>
@@ -14984,13 +15086,13 @@
         <v>9</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="D33" s="19" t="n">
         <v>55</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="F33" s="16" t="s">
         <v>37</v>
@@ -15016,13 +15118,13 @@
         <v>9</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="D34" s="19" t="n">
         <v>55</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="F34" s="16" t="s">
         <v>37</v>
@@ -15048,13 +15150,13 @@
         <v>9</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="D35" s="19" t="n">
         <v>55</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="F35" s="16" t="s">
         <v>37</v>
@@ -15080,13 +15182,13 @@
         <v>9</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="D36" s="19" t="n">
         <v>59</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="F36" s="16" t="s">
         <v>37</v>
@@ -15112,13 +15214,13 @@
         <v>9</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="D37" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="F37" s="16" t="s">
         <v>37</v>
@@ -15133,7 +15235,7 @@
         <v>40</v>
       </c>
       <c r="J37" s="18" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15144,13 +15246,13 @@
         <v>9</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="D38" s="19" t="n">
         <v>59</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="F38" s="16" t="s">
         <v>37</v>
@@ -15165,7 +15267,7 @@
         <v>40</v>
       </c>
       <c r="J38" s="18" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15176,13 +15278,13 @@
         <v>9</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="D39" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="F39" s="16" t="s">
         <v>37</v>
@@ -15208,13 +15310,13 @@
         <v>9</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="D40" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="F40" s="16" t="s">
         <v>37</v>
@@ -15240,13 +15342,13 @@
         <v>9</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="D41" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="F41" s="16" t="s">
         <v>37</v>
@@ -15261,7 +15363,7 @@
         <v>40</v>
       </c>
       <c r="J41" s="18" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15272,13 +15374,13 @@
         <v>9</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="D42" s="19" t="n">
         <v>55</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="F42" s="16" t="s">
         <v>37</v>
@@ -15304,13 +15406,13 @@
         <v>9</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="D43" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E43" s="20" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="F43" s="16" t="s">
         <v>37</v>
@@ -15336,13 +15438,13 @@
         <v>9</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="D44" s="19" t="n">
         <v>49</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="F44" s="16" t="s">
         <v>37</v>
@@ -15368,13 +15470,13 @@
         <v>9</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="D45" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="F45" s="16" t="s">
         <v>37</v>
@@ -15389,7 +15491,7 @@
         <v>40</v>
       </c>
       <c r="J45" s="18" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15400,13 +15502,13 @@
         <v>9</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="D46" s="19" t="n">
         <v>49</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="F46" s="16" t="s">
         <v>37</v>
@@ -15432,13 +15534,13 @@
         <v>9</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="D47" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="F47" s="16" t="s">
         <v>37</v>
@@ -15453,7 +15555,7 @@
         <v>40</v>
       </c>
       <c r="J47" s="18" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15464,13 +15566,13 @@
         <v>9</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="D48" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="F48" s="16" t="s">
         <v>37</v>
@@ -15496,13 +15598,13 @@
         <v>9</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="D49" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="F49" s="16" t="s">
         <v>37</v>
@@ -15528,13 +15630,13 @@
         <v>9</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="D50" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E50" s="20" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="F50" s="16" t="s">
         <v>37</v>
@@ -15560,13 +15662,13 @@
         <v>9</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="D51" s="19" t="n">
         <v>49</v>
       </c>
       <c r="E51" s="20" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="F51" s="16" t="s">
         <v>37</v>
@@ -15581,7 +15683,7 @@
         <v>40</v>
       </c>
       <c r="J51" s="18" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15592,13 +15694,13 @@
         <v>9</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="D52" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="F52" s="16" t="s">
         <v>37</v>
@@ -15624,13 +15726,13 @@
         <v>9</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="D53" s="19" t="n">
         <v>50</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="F53" s="16" t="s">
         <v>37</v>
@@ -15645,7 +15747,7 @@
         <v>40</v>
       </c>
       <c r="J53" s="18" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15656,13 +15758,13 @@
         <v>9</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="D54" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E54" s="20" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="F54" s="16" t="s">
         <v>37</v>
@@ -15688,13 +15790,13 @@
         <v>9</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="D55" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E55" s="20" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="F55" s="16" t="s">
         <v>37</v>
@@ -15709,7 +15811,7 @@
         <v>40</v>
       </c>
       <c r="J55" s="18" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15720,13 +15822,13 @@
         <v>9</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="D56" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E56" s="20" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="F56" s="16" t="s">
         <v>37</v>
@@ -15752,13 +15854,13 @@
         <v>9</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="D57" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E57" s="20" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="F57" s="16" t="s">
         <v>37</v>
@@ -15784,13 +15886,13 @@
         <v>9</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="D58" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E58" s="20" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="F58" s="16" t="s">
         <v>37</v>
@@ -15805,7 +15907,7 @@
         <v>40</v>
       </c>
       <c r="J58" s="18" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15816,13 +15918,13 @@
         <v>9</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="D59" s="19" t="n">
         <v>49</v>
       </c>
       <c r="E59" s="20" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="F59" s="16" t="s">
         <v>37</v>
@@ -15848,13 +15950,13 @@
         <v>9</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="D60" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E60" s="20" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="F60" s="16" t="s">
         <v>37</v>
@@ -15880,13 +15982,13 @@
         <v>9</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="D61" s="19" t="n">
         <v>59</v>
       </c>
       <c r="E61" s="20" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="F61" s="16" t="s">
         <v>37</v>
@@ -15912,13 +16014,13 @@
         <v>9</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="D62" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E62" s="20" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="F62" s="16" t="s">
         <v>37</v>
@@ -15944,13 +16046,13 @@
         <v>9</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="D63" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E63" s="20" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="F63" s="16" t="s">
         <v>37</v>
@@ -15965,7 +16067,7 @@
         <v>40</v>
       </c>
       <c r="J63" s="18" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15976,13 +16078,13 @@
         <v>9</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="D64" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E64" s="20" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="F64" s="16" t="s">
         <v>37</v>
@@ -15997,7 +16099,7 @@
         <v>40</v>
       </c>
       <c r="J64" s="18" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16008,13 +16110,13 @@
         <v>9</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="D65" s="19" t="n">
         <v>55</v>
       </c>
       <c r="E65" s="20" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F65" s="16" t="s">
         <v>37</v>
@@ -16040,13 +16142,13 @@
         <v>9</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="D66" s="19" t="n">
         <v>59</v>
       </c>
       <c r="E66" s="20" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="F66" s="16" t="s">
         <v>37</v>
@@ -16072,13 +16174,13 @@
         <v>9</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="D67" s="19" t="n">
         <v>59</v>
       </c>
       <c r="E67" s="20" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="F67" s="16" t="s">
         <v>37</v>
@@ -16104,13 +16206,13 @@
         <v>9</v>
       </c>
       <c r="C68" s="18" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="D68" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E68" s="20" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="F68" s="16" t="s">
         <v>37</v>
@@ -16136,13 +16238,13 @@
         <v>9</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="D69" s="19" t="n">
         <v>50</v>
       </c>
       <c r="E69" s="20" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="F69" s="16" t="s">
         <v>37</v>
@@ -16168,13 +16270,13 @@
         <v>9</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="D70" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E70" s="20" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="F70" s="16" t="s">
         <v>37</v>
@@ -16200,13 +16302,13 @@
         <v>9</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="D71" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E71" s="20" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="F71" s="16" t="s">
         <v>37</v>
@@ -16232,13 +16334,13 @@
         <v>9</v>
       </c>
       <c r="C72" s="18" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="D72" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E72" s="20" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="F72" s="16" t="s">
         <v>37</v>
@@ -16264,13 +16366,13 @@
         <v>9</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="D73" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E73" s="20" t="s">
-        <v>960</v>
+        <v>966</v>
       </c>
       <c r="F73" s="16" t="s">
         <v>37</v>
@@ -16296,13 +16398,13 @@
         <v>9</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="D74" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E74" s="20" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="F74" s="16" t="s">
         <v>37</v>
@@ -16328,13 +16430,13 @@
         <v>9</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="D75" s="19" t="n">
         <v>49</v>
       </c>
       <c r="E75" s="20" t="s">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="F75" s="16" t="s">
         <v>37</v>
@@ -16360,13 +16462,13 @@
         <v>9</v>
       </c>
       <c r="C76" s="18" t="s">
-        <v>965</v>
+        <v>971</v>
       </c>
       <c r="D76" s="19" t="n">
         <v>49</v>
       </c>
       <c r="E76" s="20" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="F76" s="16" t="s">
         <v>37</v>
@@ -16392,13 +16494,13 @@
         <v>9</v>
       </c>
       <c r="C77" s="25" t="s">
-        <v>967</v>
+        <v>973</v>
       </c>
       <c r="D77" s="19" t="n">
         <v>49</v>
       </c>
       <c r="E77" s="20" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="F77" s="16" t="s">
         <v>37</v>
@@ -16424,13 +16526,13 @@
         <v>9</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="D78" s="19" t="n">
         <v>50</v>
       </c>
       <c r="E78" s="20" t="s">
-        <v>970</v>
+        <v>976</v>
       </c>
       <c r="F78" s="16" t="s">
         <v>119</v>
@@ -16442,7 +16544,7 @@
         <v>120</v>
       </c>
       <c r="I78" s="18" t="s">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="J78" s="18" t="s">
         <v>126</v>
@@ -16456,13 +16558,13 @@
         <v>9</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="D79" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E79" s="20" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="F79" s="16" t="s">
         <v>119</v>
@@ -16474,7 +16576,7 @@
         <v>120</v>
       </c>
       <c r="I79" s="18" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="J79" s="18" t="s">
         <v>116</v>
@@ -16488,13 +16590,13 @@
         <v>9</v>
       </c>
       <c r="C80" s="18" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="D80" s="19" t="n">
         <v>50</v>
       </c>
       <c r="E80" s="20" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="F80" s="16" t="s">
         <v>119</v>
@@ -16506,7 +16608,7 @@
         <v>120</v>
       </c>
       <c r="I80" s="18" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="J80" s="18" t="s">
         <v>126</v>
@@ -16520,13 +16622,13 @@
         <v>9</v>
       </c>
       <c r="C81" s="18" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="D81" s="19" t="n">
         <v>50</v>
       </c>
       <c r="E81" s="20" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="F81" s="16" t="s">
         <v>119</v>
@@ -16552,13 +16654,13 @@
         <v>9</v>
       </c>
       <c r="C82" s="18" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="D82" s="19" t="n">
         <v>50</v>
       </c>
       <c r="E82" s="20" t="s">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="F82" s="16" t="s">
         <v>119</v>
@@ -16570,7 +16672,7 @@
         <v>120</v>
       </c>
       <c r="I82" s="18" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="J82" s="18" t="s">
         <v>126</v>
@@ -16584,13 +16686,13 @@
         <v>9</v>
       </c>
       <c r="C83" s="18" t="s">
-        <v>982</v>
+        <v>988</v>
       </c>
       <c r="D83" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E83" s="20" t="s">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="F83" s="16" t="s">
         <v>119</v>
@@ -16602,7 +16704,7 @@
         <v>120</v>
       </c>
       <c r="I83" s="18" t="s">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="J83" s="18" t="s">
         <v>116</v>
@@ -16616,13 +16718,13 @@
         <v>9</v>
       </c>
       <c r="C84" s="18" t="s">
-        <v>985</v>
+        <v>991</v>
       </c>
       <c r="D84" s="19" t="n">
         <v>50</v>
       </c>
       <c r="E84" s="20" t="s">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="F84" s="16" t="s">
         <v>119</v>
@@ -16648,13 +16750,13 @@
         <v>9</v>
       </c>
       <c r="C85" s="18" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="D85" s="19" t="n">
         <v>50</v>
       </c>
       <c r="E85" s="20" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="F85" s="16" t="s">
         <v>119</v>
@@ -16680,25 +16782,25 @@
         <v>9</v>
       </c>
       <c r="C86" s="18" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="D86" s="19" t="n">
         <v>55</v>
       </c>
       <c r="E86" s="20" t="s">
-        <v>990</v>
+        <v>996</v>
       </c>
       <c r="F86" s="16" t="s">
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="G86" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H86" s="18" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="I86" s="18" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="J86" s="18" t="s">
         <v>122</v>
@@ -16712,25 +16814,25 @@
         <v>9</v>
       </c>
       <c r="C87" s="18" t="s">
-        <v>994</v>
+        <v>1000</v>
       </c>
       <c r="D87" s="19" t="n">
         <v>55</v>
       </c>
       <c r="E87" s="20" t="s">
-        <v>995</v>
+        <v>1001</v>
       </c>
       <c r="F87" s="16" t="s">
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="G87" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H87" s="18" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="I87" s="18" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="J87" s="18" t="s">
         <v>122</v>
@@ -16744,25 +16846,25 @@
         <v>9</v>
       </c>
       <c r="C88" s="18" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
       <c r="D88" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E88" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F88" s="16" t="s">
         <v>997</v>
       </c>
-      <c r="F88" s="16" t="s">
-        <v>991</v>
-      </c>
       <c r="G88" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H88" s="18" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="I88" s="18" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="J88" s="18" t="s">
         <v>147</v>
@@ -16776,13 +16878,13 @@
         <v>9</v>
       </c>
       <c r="C89" s="18" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="D89" s="19" t="n">
         <v>50</v>
       </c>
       <c r="E89" s="20" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
       <c r="F89" s="16" t="s">
         <v>162</v>
@@ -16794,10 +16896,10 @@
         <v>163</v>
       </c>
       <c r="I89" s="18" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="J89" s="18" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16808,13 +16910,13 @@
         <v>9</v>
       </c>
       <c r="C90" s="18" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="D90" s="19" t="n">
         <v>50</v>
       </c>
       <c r="E90" s="20" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="F90" s="16" t="s">
         <v>162</v>
@@ -16840,13 +16942,13 @@
         <v>9</v>
       </c>
       <c r="C91" s="18" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="D91" s="19" t="n">
         <v>48</v>
       </c>
       <c r="E91" s="20" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
       <c r="F91" s="16" t="s">
         <v>162</v>
@@ -16858,7 +16960,7 @@
         <v>163</v>
       </c>
       <c r="I91" s="18" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="J91" s="18" t="s">
         <v>165</v>
@@ -16872,13 +16974,13 @@
         <v>9</v>
       </c>
       <c r="C92" s="18" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="D92" s="19" t="n">
         <v>50</v>
       </c>
       <c r="E92" s="20" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
       <c r="F92" s="16" t="s">
         <v>162</v>
@@ -16904,13 +17006,13 @@
         <v>9</v>
       </c>
       <c r="C93" s="18" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="D93" s="19" t="n">
         <v>55</v>
       </c>
       <c r="E93" s="20" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="F93" s="16" t="s">
         <v>162</v>
@@ -16922,7 +17024,7 @@
         <v>163</v>
       </c>
       <c r="I93" s="18" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="J93" s="18" t="s">
         <v>165</v>
@@ -16936,13 +17038,13 @@
         <v>9</v>
       </c>
       <c r="C94" s="18" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
       <c r="D94" s="19" t="n">
         <v>47</v>
       </c>
       <c r="E94" s="20" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="F94" s="16" t="s">
         <v>162</v>
@@ -16957,7 +17059,7 @@
         <v>164</v>
       </c>
       <c r="J94" s="18" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16968,13 +17070,13 @@
         <v>9</v>
       </c>
       <c r="C95" s="18" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="D95" s="19" t="n">
         <v>50</v>
       </c>
       <c r="E95" s="20" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="F95" s="16" t="s">
         <v>162</v>
@@ -17000,13 +17102,13 @@
         <v>9</v>
       </c>
       <c r="C96" s="18" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="D96" s="19" t="n">
         <v>55</v>
       </c>
       <c r="E96" s="20" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="F96" s="16" t="s">
         <v>162</v>
@@ -17032,13 +17134,13 @@
         <v>9</v>
       </c>
       <c r="C97" s="18" t="s">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="D97" s="19" t="n">
         <v>50</v>
       </c>
       <c r="E97" s="20" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="F97" s="16" t="s">
         <v>162</v>
@@ -17050,7 +17152,7 @@
         <v>163</v>
       </c>
       <c r="I97" s="18" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="J97" s="18" t="s">
         <v>165</v>
@@ -17064,13 +17166,13 @@
         <v>9</v>
       </c>
       <c r="C98" s="18" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
       <c r="D98" s="19" t="n">
         <v>55</v>
       </c>
       <c r="E98" s="20" t="s">
-        <v>1022</v>
+        <v>1028</v>
       </c>
       <c r="F98" s="16" t="s">
         <v>162</v>
@@ -17082,7 +17184,7 @@
         <v>163</v>
       </c>
       <c r="I98" s="18" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="J98" s="18" t="s">
         <v>165</v>
@@ -17096,13 +17198,13 @@
         <v>9</v>
       </c>
       <c r="C99" s="18" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="D99" s="19" t="n">
         <v>58</v>
       </c>
       <c r="E99" s="20" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
       <c r="F99" s="16" t="s">
         <v>162</v>
@@ -17128,13 +17230,13 @@
         <v>9</v>
       </c>
       <c r="C100" s="18" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="D100" s="19" t="n">
         <v>58</v>
       </c>
       <c r="E100" s="20" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
       <c r="F100" s="16" t="s">
         <v>162</v>
@@ -17146,7 +17248,7 @@
         <v>163</v>
       </c>
       <c r="I100" s="18" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="J100" s="18" t="s">
         <v>165</v>
@@ -17160,13 +17262,13 @@
         <v>9</v>
       </c>
       <c r="C101" s="18" t="s">
-        <v>1027</v>
+        <v>1033</v>
       </c>
       <c r="D101" s="19" t="n">
         <v>50</v>
       </c>
       <c r="E101" s="20" t="s">
-        <v>1028</v>
+        <v>1034</v>
       </c>
       <c r="F101" s="16" t="s">
         <v>162</v>
@@ -17178,7 +17280,7 @@
         <v>163</v>
       </c>
       <c r="I101" s="18" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="J101" s="18" t="s">
         <v>165</v>
@@ -17192,13 +17294,13 @@
         <v>9</v>
       </c>
       <c r="C102" s="18" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
       <c r="D102" s="19" t="n">
         <v>55</v>
       </c>
       <c r="E102" s="20" t="s">
-        <v>1030</v>
+        <v>1036</v>
       </c>
       <c r="F102" s="16" t="s">
         <v>162</v>
@@ -17210,7 +17312,7 @@
         <v>163</v>
       </c>
       <c r="I102" s="18" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="J102" s="18" t="s">
         <v>165</v>
@@ -17224,13 +17326,13 @@
         <v>9</v>
       </c>
       <c r="C103" s="18" t="s">
-        <v>1031</v>
+        <v>1037</v>
       </c>
       <c r="D103" s="19" t="n">
         <v>58</v>
       </c>
       <c r="E103" s="20" t="s">
-        <v>1032</v>
+        <v>1038</v>
       </c>
       <c r="F103" s="16" t="s">
         <v>162</v>
@@ -17256,13 +17358,13 @@
         <v>9</v>
       </c>
       <c r="C104" s="18" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="D104" s="19" t="n">
         <v>48</v>
       </c>
       <c r="E104" s="20" t="s">
-        <v>1034</v>
+        <v>1040</v>
       </c>
       <c r="F104" s="16" t="s">
         <v>162</v>
@@ -17288,13 +17390,13 @@
         <v>9</v>
       </c>
       <c r="C105" s="18" t="s">
-        <v>1035</v>
+        <v>1041</v>
       </c>
       <c r="D105" s="19" t="n">
         <v>50</v>
       </c>
       <c r="E105" s="20" t="s">
-        <v>1036</v>
+        <v>1042</v>
       </c>
       <c r="F105" s="16" t="s">
         <v>162</v>
@@ -17320,13 +17422,13 @@
         <v>9</v>
       </c>
       <c r="C106" s="18" t="s">
-        <v>1037</v>
+        <v>1043</v>
       </c>
       <c r="D106" s="19" t="n">
         <v>55</v>
       </c>
       <c r="E106" s="20" t="s">
-        <v>1038</v>
+        <v>1044</v>
       </c>
       <c r="F106" s="16" t="s">
         <v>162</v>
@@ -17352,13 +17454,13 @@
         <v>9</v>
       </c>
       <c r="C107" s="18" t="s">
-        <v>1039</v>
+        <v>1045</v>
       </c>
       <c r="D107" s="19" t="n">
         <v>55</v>
       </c>
       <c r="E107" s="20" t="s">
-        <v>1040</v>
+        <v>1046</v>
       </c>
       <c r="F107" s="16" t="s">
         <v>162</v>
@@ -17370,10 +17472,10 @@
         <v>163</v>
       </c>
       <c r="I107" s="18" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="J107" s="18" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17384,13 +17486,13 @@
         <v>9</v>
       </c>
       <c r="C108" s="18" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="D108" s="19" t="n">
         <v>50</v>
       </c>
       <c r="E108" s="20" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
       <c r="F108" s="16" t="s">
         <v>162</v>
@@ -17402,10 +17504,10 @@
         <v>163</v>
       </c>
       <c r="I108" s="18" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="J108" s="18" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17416,13 +17518,13 @@
         <v>9</v>
       </c>
       <c r="C109" s="18" t="s">
-        <v>1043</v>
+        <v>1049</v>
       </c>
       <c r="D109" s="19" t="n">
         <v>50</v>
       </c>
       <c r="E109" s="20" t="s">
-        <v>1044</v>
+        <v>1050</v>
       </c>
       <c r="F109" s="16" t="s">
         <v>162</v>
@@ -17448,13 +17550,13 @@
         <v>9</v>
       </c>
       <c r="C110" s="18" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="D110" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E110" s="20" t="s">
-        <v>1046</v>
+        <v>1052</v>
       </c>
       <c r="F110" s="16" t="s">
         <v>162</v>
@@ -17466,7 +17568,7 @@
         <v>163</v>
       </c>
       <c r="I110" s="18" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="J110" s="18" t="s">
         <v>165</v>
@@ -17480,13 +17582,13 @@
         <v>9</v>
       </c>
       <c r="C111" s="18" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="D111" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E111" s="20" t="s">
-        <v>1048</v>
+        <v>1054</v>
       </c>
       <c r="F111" s="16" t="s">
         <v>162</v>
@@ -17498,7 +17600,7 @@
         <v>163</v>
       </c>
       <c r="I111" s="18" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="J111" s="18" t="s">
         <v>165</v>
@@ -17512,13 +17614,13 @@
         <v>9</v>
       </c>
       <c r="C112" s="18" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
       <c r="D112" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E112" s="20" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="F112" s="16" t="s">
         <v>162</v>
@@ -17544,13 +17646,13 @@
         <v>9</v>
       </c>
       <c r="C113" s="18" t="s">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="D113" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E113" s="20" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="F113" s="16" t="s">
         <v>162</v>
@@ -17562,7 +17664,7 @@
         <v>163</v>
       </c>
       <c r="I113" s="18" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="J113" s="18" t="s">
         <v>165</v>
@@ -17576,13 +17678,13 @@
         <v>9</v>
       </c>
       <c r="C114" s="18" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="D114" s="19" t="n">
         <v>55</v>
       </c>
       <c r="E114" s="20" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="F114" s="16" t="s">
         <v>168</v>
@@ -17597,7 +17699,7 @@
         <v>169</v>
       </c>
       <c r="J114" s="18" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17608,13 +17710,13 @@
         <v>9</v>
       </c>
       <c r="C115" s="18" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="D115" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E115" s="20" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="F115" s="16" t="s">
         <v>168</v>
@@ -17629,7 +17731,7 @@
         <v>169</v>
       </c>
       <c r="J115" s="18" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17640,13 +17742,13 @@
         <v>9</v>
       </c>
       <c r="C116" s="18" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="D116" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E116" s="20" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="F116" s="16" t="s">
         <v>168</v>
@@ -17661,7 +17763,7 @@
         <v>169</v>
       </c>
       <c r="J116" s="18" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17672,13 +17774,13 @@
         <v>9</v>
       </c>
       <c r="C117" s="18" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="D117" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E117" s="20" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="F117" s="16" t="s">
         <v>168</v>
@@ -17693,7 +17795,7 @@
         <v>169</v>
       </c>
       <c r="J117" s="18" t="s">
-        <v>1065</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17704,13 +17806,13 @@
         <v>9</v>
       </c>
       <c r="C118" s="18" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
       <c r="D118" s="19" t="n">
         <v>50</v>
       </c>
       <c r="E118" s="20" t="s">
-        <v>1067</v>
+        <v>1073</v>
       </c>
       <c r="F118" s="16" t="s">
         <v>168</v>
@@ -17725,7 +17827,7 @@
         <v>169</v>
       </c>
       <c r="J118" s="18" t="s">
-        <v>1068</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17736,13 +17838,13 @@
         <v>9</v>
       </c>
       <c r="C119" s="18" t="s">
-        <v>1069</v>
+        <v>1075</v>
       </c>
       <c r="D119" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E119" s="20" t="s">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="F119" s="16" t="s">
         <v>168</v>
@@ -17757,7 +17859,7 @@
         <v>169</v>
       </c>
       <c r="J119" s="18" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17768,13 +17870,13 @@
         <v>9</v>
       </c>
       <c r="C120" s="18" t="s">
-        <v>1071</v>
+        <v>1077</v>
       </c>
       <c r="D120" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E120" s="20" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="F120" s="16" t="s">
         <v>168</v>
@@ -17789,7 +17891,7 @@
         <v>169</v>
       </c>
       <c r="J120" s="18" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17800,13 +17902,13 @@
         <v>9</v>
       </c>
       <c r="C121" s="18" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="D121" s="19" t="n">
         <v>55</v>
       </c>
       <c r="E121" s="20" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
       <c r="F121" s="16" t="s">
         <v>168</v>
@@ -17821,7 +17923,7 @@
         <v>169</v>
       </c>
       <c r="J121" s="18" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17832,13 +17934,13 @@
         <v>9</v>
       </c>
       <c r="C122" s="18" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
       <c r="D122" s="19" t="n">
         <v>55</v>
       </c>
       <c r="E122" s="20" t="s">
-        <v>1077</v>
+        <v>1083</v>
       </c>
       <c r="F122" s="16" t="s">
         <v>168</v>
@@ -17853,7 +17955,7 @@
         <v>169</v>
       </c>
       <c r="J122" s="18" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17864,13 +17966,13 @@
         <v>9</v>
       </c>
       <c r="C123" s="18" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
       <c r="D123" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E123" s="20" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="F123" s="16" t="s">
         <v>168</v>
@@ -17885,7 +17987,7 @@
         <v>169</v>
       </c>
       <c r="J123" s="18" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17896,13 +17998,13 @@
         <v>9</v>
       </c>
       <c r="C124" s="18" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
       <c r="D124" s="19" t="n">
         <v>49</v>
       </c>
       <c r="E124" s="20" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="F124" s="16" t="s">
         <v>197</v>
@@ -17928,13 +18030,13 @@
         <v>9</v>
       </c>
       <c r="C125" s="18" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="D125" s="19" t="n">
         <v>53</v>
       </c>
       <c r="E125" s="20" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="F125" s="16" t="s">
         <v>197</v>
@@ -17960,13 +18062,13 @@
         <v>9</v>
       </c>
       <c r="C126" s="18" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="D126" s="19" t="n">
         <v>49</v>
       </c>
       <c r="E126" s="20" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="F126" s="16" t="s">
         <v>197</v>
@@ -17992,13 +18094,13 @@
         <v>9</v>
       </c>
       <c r="C127" s="18" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="D127" s="19" t="n">
         <v>49</v>
       </c>
       <c r="E127" s="20" t="s">
-        <v>1088</v>
+        <v>1094</v>
       </c>
       <c r="F127" s="16" t="s">
         <v>197</v>
@@ -18024,13 +18126,13 @@
         <v>9</v>
       </c>
       <c r="C128" s="18" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="D128" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E128" s="20" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
       <c r="F128" s="16" t="s">
         <v>197</v>
@@ -18056,13 +18158,13 @@
         <v>9</v>
       </c>
       <c r="C129" s="18" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
       <c r="D129" s="19" t="n">
         <v>56</v>
       </c>
       <c r="E129" s="20" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
       <c r="F129" s="16" t="s">
         <v>197</v>
@@ -18088,13 +18190,13 @@
         <v>9</v>
       </c>
       <c r="C130" s="18" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="D130" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E130" s="20" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
       <c r="F130" s="16" t="s">
         <v>197</v>
@@ -18120,13 +18222,13 @@
         <v>9</v>
       </c>
       <c r="C131" s="18" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="D131" s="19" t="n">
         <v>49</v>
       </c>
       <c r="E131" s="20" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="F131" s="16" t="s">
         <v>197</v>
@@ -18152,13 +18254,13 @@
         <v>9</v>
       </c>
       <c r="C132" s="18" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="D132" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E132" s="20" t="s">
-        <v>1098</v>
+        <v>1104</v>
       </c>
       <c r="F132" s="16" t="s">
         <v>197</v>
@@ -18184,13 +18286,13 @@
         <v>9</v>
       </c>
       <c r="C133" s="18" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
       <c r="D133" s="19" t="n">
         <v>56</v>
       </c>
       <c r="E133" s="20" t="s">
-        <v>1100</v>
+        <v>1106</v>
       </c>
       <c r="F133" s="16" t="s">
         <v>197</v>
@@ -18216,13 +18318,13 @@
         <v>9</v>
       </c>
       <c r="C134" s="18" t="s">
-        <v>1101</v>
+        <v>1107</v>
       </c>
       <c r="D134" s="19" t="n">
         <v>49</v>
       </c>
       <c r="E134" s="20" t="s">
-        <v>1102</v>
+        <v>1108</v>
       </c>
       <c r="F134" s="16" t="s">
         <v>197</v>
@@ -18248,13 +18350,13 @@
         <v>9</v>
       </c>
       <c r="C135" s="18" t="s">
-        <v>1103</v>
+        <v>1109</v>
       </c>
       <c r="D135" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E135" s="20" t="s">
-        <v>1104</v>
+        <v>1110</v>
       </c>
       <c r="F135" s="16" t="s">
         <v>197</v>
@@ -18280,13 +18382,13 @@
         <v>9</v>
       </c>
       <c r="C136" s="18" t="s">
-        <v>1105</v>
+        <v>1111</v>
       </c>
       <c r="D136" s="19" t="n">
         <v>53</v>
       </c>
       <c r="E136" s="20" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="F136" s="16" t="s">
         <v>197</v>
@@ -18312,13 +18414,13 @@
         <v>9</v>
       </c>
       <c r="C137" s="18" t="s">
-        <v>1107</v>
+        <v>1113</v>
       </c>
       <c r="D137" s="19" t="n">
         <v>56</v>
       </c>
       <c r="E137" s="20" t="s">
-        <v>1108</v>
+        <v>1114</v>
       </c>
       <c r="F137" s="16" t="s">
         <v>197</v>
@@ -18344,13 +18446,13 @@
         <v>9</v>
       </c>
       <c r="C138" s="18" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="D138" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E138" s="20" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
       <c r="F138" s="16" t="s">
         <v>197</v>
@@ -18376,13 +18478,13 @@
         <v>9</v>
       </c>
       <c r="C139" s="18" t="s">
-        <v>1111</v>
+        <v>1117</v>
       </c>
       <c r="D139" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E139" s="20" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="F139" s="16" t="s">
         <v>197</v>
@@ -18408,13 +18510,13 @@
         <v>9</v>
       </c>
       <c r="C140" s="18" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
       <c r="D140" s="19" t="n">
         <v>49</v>
       </c>
       <c r="E140" s="20" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="F140" s="16" t="s">
         <v>197</v>
@@ -18440,13 +18542,13 @@
         <v>9</v>
       </c>
       <c r="C141" s="18" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="D141" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E141" s="20" t="s">
-        <v>1116</v>
+        <v>1122</v>
       </c>
       <c r="F141" s="16" t="s">
         <v>197</v>
@@ -18472,13 +18574,13 @@
         <v>9</v>
       </c>
       <c r="C142" s="18" t="s">
-        <v>1117</v>
+        <v>1123</v>
       </c>
       <c r="D142" s="19" t="n">
         <v>49</v>
       </c>
       <c r="E142" s="20" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="F142" s="16" t="s">
         <v>197</v>
@@ -18504,13 +18606,13 @@
         <v>9</v>
       </c>
       <c r="C143" s="18" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
       <c r="D143" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E143" s="20" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="F143" s="16" t="s">
         <v>197</v>
@@ -18536,13 +18638,13 @@
         <v>9</v>
       </c>
       <c r="C144" s="18" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="D144" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E144" s="20" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
       <c r="F144" s="16" t="s">
         <v>197</v>
@@ -18568,13 +18670,13 @@
         <v>9</v>
       </c>
       <c r="C145" s="18" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
       <c r="D145" s="19" t="n">
         <v>53</v>
       </c>
       <c r="E145" s="20" t="s">
-        <v>1124</v>
+        <v>1130</v>
       </c>
       <c r="F145" s="16" t="s">
         <v>197</v>
@@ -18600,13 +18702,13 @@
         <v>9</v>
       </c>
       <c r="C146" s="18" t="s">
-        <v>1125</v>
+        <v>1131</v>
       </c>
       <c r="D146" s="19" t="n">
         <v>57</v>
       </c>
       <c r="E146" s="20" t="s">
-        <v>1126</v>
+        <v>1132</v>
       </c>
       <c r="F146" s="16" t="s">
         <v>197</v>
@@ -18621,7 +18723,7 @@
         <v>200</v>
       </c>
       <c r="J146" s="18" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18632,13 +18734,13 @@
         <v>9</v>
       </c>
       <c r="C147" s="18" t="s">
-        <v>1127</v>
+        <v>1133</v>
       </c>
       <c r="D147" s="19" t="n">
         <v>53</v>
       </c>
       <c r="E147" s="20" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
       <c r="F147" s="16" t="s">
         <v>197</v>
@@ -18664,13 +18766,13 @@
         <v>9</v>
       </c>
       <c r="C148" s="18" t="s">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="D148" s="19" t="n">
         <v>56</v>
       </c>
       <c r="E148" s="20" t="s">
-        <v>1130</v>
+        <v>1136</v>
       </c>
       <c r="F148" s="16" t="s">
         <v>197</v>
@@ -18696,13 +18798,13 @@
         <v>9</v>
       </c>
       <c r="C149" s="18" t="s">
-        <v>1131</v>
+        <v>1137</v>
       </c>
       <c r="D149" s="19" t="n">
         <v>53</v>
       </c>
       <c r="E149" s="20" t="s">
-        <v>1132</v>
+        <v>1138</v>
       </c>
       <c r="F149" s="16" t="s">
         <v>197</v>
@@ -18728,13 +18830,13 @@
         <v>9</v>
       </c>
       <c r="C150" s="18" t="s">
-        <v>1133</v>
+        <v>1139</v>
       </c>
       <c r="D150" s="19" t="n">
         <v>49</v>
       </c>
       <c r="E150" s="20" t="s">
-        <v>1134</v>
+        <v>1140</v>
       </c>
       <c r="F150" s="16" t="s">
         <v>197</v>
@@ -18760,13 +18862,13 @@
         <v>9</v>
       </c>
       <c r="C151" s="18" t="s">
-        <v>1135</v>
+        <v>1141</v>
       </c>
       <c r="D151" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E151" s="20" t="s">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="F151" s="16" t="s">
         <v>197</v>
@@ -18792,13 +18894,13 @@
         <v>9</v>
       </c>
       <c r="C152" s="18" t="s">
-        <v>1137</v>
+        <v>1143</v>
       </c>
       <c r="D152" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E152" s="20" t="s">
-        <v>1138</v>
+        <v>1144</v>
       </c>
       <c r="F152" s="16" t="s">
         <v>197</v>
@@ -18824,13 +18926,13 @@
         <v>10</v>
       </c>
       <c r="C153" s="18" t="s">
-        <v>1139</v>
+        <v>1145</v>
       </c>
       <c r="D153" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E153" s="20" t="s">
-        <v>1140</v>
+        <v>1146</v>
       </c>
       <c r="F153" s="16" t="s">
         <v>772</v>
@@ -18839,13 +18941,13 @@
         <v>38</v>
       </c>
       <c r="H153" s="18" t="s">
-        <v>1141</v>
+        <v>1147</v>
       </c>
       <c r="I153" s="18" t="s">
-        <v>1142</v>
+        <v>1148</v>
       </c>
       <c r="J153" s="18" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18856,13 +18958,13 @@
         <v>10</v>
       </c>
       <c r="C154" s="18" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="D154" s="19" t="n">
         <v>55</v>
       </c>
       <c r="E154" s="20" t="s">
-        <v>1145</v>
+        <v>1151</v>
       </c>
       <c r="F154" s="16" t="s">
         <v>299</v>
@@ -18877,7 +18979,7 @@
         <v>301</v>
       </c>
       <c r="J154" s="18" t="s">
-        <v>1146</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18888,13 +18990,13 @@
         <v>10</v>
       </c>
       <c r="C155" s="18" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
       <c r="D155" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E155" s="20" t="s">
-        <v>1148</v>
+        <v>1154</v>
       </c>
       <c r="F155" s="16" t="s">
         <v>299</v>
@@ -18909,7 +19011,7 @@
         <v>301</v>
       </c>
       <c r="J155" s="18" t="s">
-        <v>1149</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18920,13 +19022,13 @@
         <v>10</v>
       </c>
       <c r="C156" s="18" t="s">
-        <v>1150</v>
+        <v>1156</v>
       </c>
       <c r="D156" s="19" t="n">
         <v>55</v>
       </c>
       <c r="E156" s="20" t="s">
-        <v>1151</v>
+        <v>1157</v>
       </c>
       <c r="F156" s="16" t="s">
         <v>299</v>
@@ -18941,7 +19043,7 @@
         <v>301</v>
       </c>
       <c r="J156" s="18" t="s">
-        <v>1152</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18952,13 +19054,13 @@
         <v>10</v>
       </c>
       <c r="C157" s="18" t="s">
-        <v>1153</v>
+        <v>1159</v>
       </c>
       <c r="D157" s="19" t="n">
         <v>55</v>
       </c>
       <c r="E157" s="20" t="s">
-        <v>1154</v>
+        <v>1160</v>
       </c>
       <c r="F157" s="16" t="s">
         <v>299</v>
@@ -18973,7 +19075,7 @@
         <v>301</v>
       </c>
       <c r="J157" s="18" t="s">
-        <v>1155</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18984,13 +19086,13 @@
         <v>10</v>
       </c>
       <c r="C158" s="18" t="s">
-        <v>1156</v>
+        <v>1162</v>
       </c>
       <c r="D158" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E158" s="20" t="s">
-        <v>1157</v>
+        <v>1163</v>
       </c>
       <c r="F158" s="16" t="s">
         <v>299</v>
@@ -19005,7 +19107,7 @@
         <v>301</v>
       </c>
       <c r="J158" s="18" t="s">
-        <v>1158</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19016,13 +19118,13 @@
         <v>10</v>
       </c>
       <c r="C159" s="18" t="s">
-        <v>1159</v>
+        <v>1165</v>
       </c>
       <c r="D159" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E159" s="20" t="s">
-        <v>1160</v>
+        <v>1166</v>
       </c>
       <c r="F159" s="16" t="s">
         <v>299</v>
@@ -19037,7 +19139,7 @@
         <v>301</v>
       </c>
       <c r="J159" s="18" t="s">
-        <v>1161</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19048,13 +19150,13 @@
         <v>10</v>
       </c>
       <c r="C160" s="18" t="s">
-        <v>1162</v>
+        <v>1168</v>
       </c>
       <c r="D160" s="19" t="n">
         <v>50</v>
       </c>
       <c r="E160" s="20" t="s">
-        <v>1163</v>
+        <v>1169</v>
       </c>
       <c r="F160" s="16" t="s">
         <v>299</v>
@@ -19069,7 +19171,7 @@
         <v>301</v>
       </c>
       <c r="J160" s="18" t="s">
-        <v>1164</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19080,13 +19182,13 @@
         <v>10</v>
       </c>
       <c r="C161" s="18" t="s">
-        <v>1165</v>
+        <v>1171</v>
       </c>
       <c r="D161" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E161" s="20" t="s">
-        <v>1166</v>
+        <v>1172</v>
       </c>
       <c r="F161" s="16" t="s">
         <v>299</v>
@@ -19101,7 +19203,7 @@
         <v>301</v>
       </c>
       <c r="J161" s="18" t="s">
-        <v>1167</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19112,13 +19214,13 @@
         <v>10</v>
       </c>
       <c r="C162" s="18" t="s">
-        <v>1168</v>
+        <v>1174</v>
       </c>
       <c r="D162" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E162" s="20" t="s">
-        <v>1169</v>
+        <v>1175</v>
       </c>
       <c r="F162" s="16" t="s">
         <v>299</v>
@@ -19133,7 +19235,7 @@
         <v>301</v>
       </c>
       <c r="J162" s="18" t="s">
-        <v>1170</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19144,13 +19246,13 @@
         <v>10</v>
       </c>
       <c r="C163" s="18" t="s">
-        <v>1171</v>
+        <v>1177</v>
       </c>
       <c r="D163" s="19" t="n">
         <v>50</v>
       </c>
       <c r="E163" s="20" t="s">
-        <v>1172</v>
+        <v>1178</v>
       </c>
       <c r="F163" s="16" t="s">
         <v>299</v>
@@ -19165,7 +19267,7 @@
         <v>301</v>
       </c>
       <c r="J163" s="18" t="s">
-        <v>1173</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19176,13 +19278,13 @@
         <v>10</v>
       </c>
       <c r="C164" s="18" t="s">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="D164" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E164" s="20" t="s">
-        <v>1175</v>
+        <v>1181</v>
       </c>
       <c r="F164" s="16" t="s">
         <v>299</v>
@@ -19197,7 +19299,7 @@
         <v>301</v>
       </c>
       <c r="J164" s="18" t="s">
-        <v>1176</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19208,13 +19310,13 @@
         <v>10</v>
       </c>
       <c r="C165" s="18" t="s">
-        <v>1177</v>
+        <v>1183</v>
       </c>
       <c r="D165" s="19" t="n">
         <v>55</v>
       </c>
       <c r="E165" s="20" t="s">
-        <v>1178</v>
+        <v>1184</v>
       </c>
       <c r="F165" s="16" t="s">
         <v>299</v>
@@ -19229,7 +19331,7 @@
         <v>301</v>
       </c>
       <c r="J165" s="18" t="s">
-        <v>1179</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19240,13 +19342,13 @@
         <v>10</v>
       </c>
       <c r="C166" s="18" t="s">
-        <v>1180</v>
+        <v>1186</v>
       </c>
       <c r="D166" s="19" t="n">
         <v>50</v>
       </c>
       <c r="E166" s="20" t="s">
-        <v>1181</v>
+        <v>1187</v>
       </c>
       <c r="F166" s="16" t="s">
         <v>458</v>
@@ -19258,10 +19360,10 @@
         <v>459</v>
       </c>
       <c r="I166" s="18" t="s">
-        <v>1182</v>
+        <v>1188</v>
       </c>
       <c r="J166" s="18" t="s">
-        <v>1183</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19272,13 +19374,13 @@
         <v>11</v>
       </c>
       <c r="C167" s="18" t="s">
-        <v>1184</v>
+        <v>1190</v>
       </c>
       <c r="D167" s="19" t="n">
         <v>59</v>
       </c>
       <c r="E167" s="20" t="s">
-        <v>1185</v>
+        <v>1191</v>
       </c>
       <c r="F167" s="16" t="s">
         <v>598</v>
@@ -19290,7 +19392,7 @@
         <v>600</v>
       </c>
       <c r="I167" s="18" t="s">
-        <v>1186</v>
+        <v>1192</v>
       </c>
       <c r="J167" s="18" t="s">
         <v>710</v>
@@ -19304,13 +19406,13 @@
         <v>11</v>
       </c>
       <c r="C168" s="18" t="s">
-        <v>1187</v>
+        <v>1193</v>
       </c>
       <c r="D168" s="19" t="n">
         <v>59</v>
       </c>
       <c r="E168" s="20" t="s">
-        <v>1188</v>
+        <v>1194</v>
       </c>
       <c r="F168" s="16" t="s">
         <v>598</v>
@@ -19322,7 +19424,7 @@
         <v>600</v>
       </c>
       <c r="I168" s="18" t="s">
-        <v>1189</v>
+        <v>1195</v>
       </c>
       <c r="J168" s="18" t="s">
         <v>710</v>
@@ -19336,13 +19438,13 @@
         <v>11</v>
       </c>
       <c r="C169" s="18" t="s">
-        <v>1190</v>
+        <v>1196</v>
       </c>
       <c r="D169" s="19" t="n">
         <v>59</v>
       </c>
       <c r="E169" s="20" t="s">
-        <v>1191</v>
+        <v>1197</v>
       </c>
       <c r="F169" s="16" t="s">
         <v>598</v>
@@ -19354,7 +19456,7 @@
         <v>600</v>
       </c>
       <c r="I169" s="18" t="s">
-        <v>1192</v>
+        <v>1198</v>
       </c>
       <c r="J169" s="18" t="s">
         <v>710</v>
@@ -19368,28 +19470,28 @@
         <v>11</v>
       </c>
       <c r="C170" s="18" t="s">
-        <v>1193</v>
+        <v>1199</v>
       </c>
       <c r="D170" s="19" t="n">
         <v>57.1</v>
       </c>
       <c r="E170" s="20" t="s">
-        <v>1194</v>
+        <v>1200</v>
       </c>
       <c r="F170" s="16" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="G170" s="16" t="s">
         <v>198</v>
       </c>
       <c r="H170" s="18" t="s">
-        <v>1196</v>
+        <v>1202</v>
       </c>
       <c r="I170" s="18" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
       <c r="J170" s="18" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19400,28 +19502,28 @@
         <v>11</v>
       </c>
       <c r="C171" s="18" t="s">
-        <v>1199</v>
+        <v>1205</v>
       </c>
       <c r="D171" s="19" t="n">
         <v>57.1</v>
       </c>
       <c r="E171" s="20" t="s">
-        <v>1200</v>
+        <v>1206</v>
       </c>
       <c r="F171" s="16" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="G171" s="16" t="s">
         <v>198</v>
       </c>
       <c r="H171" s="18" t="s">
-        <v>1196</v>
+        <v>1202</v>
       </c>
       <c r="I171" s="18" t="s">
-        <v>1201</v>
+        <v>1207</v>
       </c>
       <c r="J171" s="18" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19432,28 +19534,28 @@
         <v>11</v>
       </c>
       <c r="C172" s="18" t="s">
-        <v>1202</v>
+        <v>1208</v>
       </c>
       <c r="D172" s="19" t="n">
         <v>57.1</v>
       </c>
       <c r="E172" s="20" t="s">
-        <v>1203</v>
+        <v>1209</v>
       </c>
       <c r="F172" s="16" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="G172" s="16" t="s">
         <v>198</v>
       </c>
       <c r="H172" s="18" t="s">
-        <v>1196</v>
+        <v>1202</v>
       </c>
       <c r="I172" s="18" t="s">
+        <v>1210</v>
+      </c>
+      <c r="J172" s="18" t="s">
         <v>1204</v>
-      </c>
-      <c r="J172" s="18" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19464,28 +19566,28 @@
         <v>11</v>
       </c>
       <c r="C173" s="18" t="s">
-        <v>1205</v>
+        <v>1211</v>
       </c>
       <c r="D173" s="19" t="n">
         <v>57.1</v>
       </c>
       <c r="E173" s="20" t="s">
-        <v>1206</v>
+        <v>1212</v>
       </c>
       <c r="F173" s="16" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="G173" s="16" t="s">
         <v>198</v>
       </c>
       <c r="H173" s="18" t="s">
-        <v>1196</v>
+        <v>1202</v>
       </c>
       <c r="I173" s="18" t="s">
-        <v>1207</v>
+        <v>1213</v>
       </c>
       <c r="J173" s="18" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19496,28 +19598,28 @@
         <v>11</v>
       </c>
       <c r="C174" s="18" t="s">
-        <v>1208</v>
+        <v>1214</v>
       </c>
       <c r="D174" s="19" t="n">
         <v>57.1</v>
       </c>
       <c r="E174" s="20" t="s">
-        <v>1209</v>
+        <v>1215</v>
       </c>
       <c r="F174" s="16" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="G174" s="16" t="s">
         <v>198</v>
       </c>
       <c r="H174" s="18" t="s">
-        <v>1196</v>
+        <v>1202</v>
       </c>
       <c r="I174" s="18" t="s">
-        <v>1210</v>
+        <v>1216</v>
       </c>
       <c r="J174" s="18" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19528,28 +19630,28 @@
         <v>11</v>
       </c>
       <c r="C175" s="18" t="s">
-        <v>1211</v>
+        <v>1217</v>
       </c>
       <c r="D175" s="19" t="n">
         <v>57.1</v>
       </c>
       <c r="E175" s="20" t="s">
-        <v>1212</v>
+        <v>1218</v>
       </c>
       <c r="F175" s="16" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="G175" s="16" t="s">
         <v>198</v>
       </c>
       <c r="H175" s="18" t="s">
-        <v>1196</v>
+        <v>1202</v>
       </c>
       <c r="I175" s="18" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="J175" s="18" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19560,28 +19662,28 @@
         <v>11</v>
       </c>
       <c r="C176" s="18" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="D176" s="19" t="n">
         <v>57.1</v>
       </c>
       <c r="E176" s="20" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
       <c r="F176" s="16" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="G176" s="16" t="s">
         <v>198</v>
       </c>
       <c r="H176" s="18" t="s">
-        <v>1196</v>
+        <v>1202</v>
       </c>
       <c r="I176" s="18" t="s">
-        <v>1216</v>
+        <v>1222</v>
       </c>
       <c r="J176" s="18" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19592,28 +19694,28 @@
         <v>11</v>
       </c>
       <c r="C177" s="18" t="s">
-        <v>1217</v>
+        <v>1223</v>
       </c>
       <c r="D177" s="19" t="n">
         <v>57.1</v>
       </c>
       <c r="E177" s="20" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="F177" s="16" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="G177" s="16" t="s">
         <v>198</v>
       </c>
       <c r="H177" s="18" t="s">
-        <v>1196</v>
+        <v>1202</v>
       </c>
       <c r="I177" s="18" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="J177" s="18" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19624,28 +19726,28 @@
         <v>11</v>
       </c>
       <c r="C178" s="18" t="s">
-        <v>1220</v>
+        <v>1226</v>
       </c>
       <c r="D178" s="19" t="n">
         <v>57.1</v>
       </c>
       <c r="E178" s="20" t="s">
-        <v>1221</v>
+        <v>1227</v>
       </c>
       <c r="F178" s="16" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="G178" s="16" t="s">
         <v>198</v>
       </c>
       <c r="H178" s="18" t="s">
-        <v>1196</v>
+        <v>1202</v>
       </c>
       <c r="I178" s="18" t="s">
-        <v>1222</v>
+        <v>1228</v>
       </c>
       <c r="J178" s="18" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19656,28 +19758,28 @@
         <v>11</v>
       </c>
       <c r="C179" s="18" t="s">
-        <v>1223</v>
+        <v>1229</v>
       </c>
       <c r="D179" s="19" t="n">
         <v>57.1</v>
       </c>
       <c r="E179" s="20" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="F179" s="16" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="G179" s="16" t="s">
         <v>198</v>
       </c>
       <c r="H179" s="18" t="s">
-        <v>1196</v>
+        <v>1202</v>
       </c>
       <c r="I179" s="18" t="s">
-        <v>1225</v>
+        <v>1231</v>
       </c>
       <c r="J179" s="18" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19688,13 +19790,13 @@
         <v>13</v>
       </c>
       <c r="C180" s="18" t="s">
-        <v>1226</v>
+        <v>1232</v>
       </c>
       <c r="D180" s="19" t="n">
         <v>49.9</v>
       </c>
       <c r="E180" s="20" t="s">
-        <v>1227</v>
+        <v>1233</v>
       </c>
       <c r="F180" s="16" t="s">
         <v>726</v>
@@ -19709,7 +19811,7 @@
         <v>728</v>
       </c>
       <c r="J180" s="18" t="s">
-        <v>1228</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19720,13 +19822,13 @@
         <v>13</v>
       </c>
       <c r="C181" s="18" t="s">
-        <v>1229</v>
+        <v>1235</v>
       </c>
       <c r="D181" s="19" t="n">
         <v>54.9</v>
       </c>
       <c r="E181" s="20" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="F181" s="16" t="s">
         <v>726</v>
@@ -19741,7 +19843,7 @@
         <v>728</v>
       </c>
       <c r="J181" s="18" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19752,13 +19854,13 @@
         <v>13</v>
       </c>
       <c r="C182" s="18" t="s">
-        <v>1232</v>
+        <v>1238</v>
       </c>
       <c r="D182" s="19" t="n">
         <v>59.9</v>
       </c>
       <c r="E182" s="20" t="s">
-        <v>1233</v>
+        <v>1239</v>
       </c>
       <c r="F182" s="16" t="s">
         <v>726</v>
@@ -19773,7 +19875,7 @@
         <v>728</v>
       </c>
       <c r="J182" s="18" t="s">
-        <v>1234</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19784,13 +19886,13 @@
         <v>13</v>
       </c>
       <c r="C183" s="18" t="s">
-        <v>1235</v>
+        <v>1241</v>
       </c>
       <c r="D183" s="19" t="n">
         <v>54.9</v>
       </c>
       <c r="E183" s="20" t="s">
-        <v>1236</v>
+        <v>1242</v>
       </c>
       <c r="F183" s="16" t="s">
         <v>726</v>
@@ -19805,7 +19907,7 @@
         <v>728</v>
       </c>
       <c r="J183" s="18" t="s">
-        <v>1237</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19816,13 +19918,13 @@
         <v>13</v>
       </c>
       <c r="C184" s="18" t="s">
-        <v>1238</v>
+        <v>1244</v>
       </c>
       <c r="D184" s="19" t="n">
         <v>49.9</v>
       </c>
       <c r="E184" s="20" t="s">
-        <v>1239</v>
+        <v>1245</v>
       </c>
       <c r="F184" s="16" t="s">
         <v>726</v>
@@ -19837,7 +19939,7 @@
         <v>728</v>
       </c>
       <c r="J184" s="18" t="s">
-        <v>1240</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19848,13 +19950,13 @@
         <v>13</v>
       </c>
       <c r="C185" s="18" t="s">
-        <v>1241</v>
+        <v>1247</v>
       </c>
       <c r="D185" s="19" t="n">
         <v>49.9</v>
       </c>
       <c r="E185" s="20" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="F185" s="16" t="s">
         <v>726</v>
@@ -19869,7 +19971,7 @@
         <v>728</v>
       </c>
       <c r="J185" s="18" t="s">
-        <v>1243</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19880,13 +19982,13 @@
         <v>13</v>
       </c>
       <c r="C186" s="18" t="s">
-        <v>1244</v>
+        <v>1250</v>
       </c>
       <c r="D186" s="19" t="n">
         <v>59.9</v>
       </c>
       <c r="E186" s="20" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="F186" s="16" t="s">
         <v>726</v>
@@ -19901,7 +20003,7 @@
         <v>728</v>
       </c>
       <c r="J186" s="18" t="s">
-        <v>1246</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19912,13 +20014,13 @@
         <v>13</v>
       </c>
       <c r="C187" s="18" t="s">
-        <v>1247</v>
+        <v>1253</v>
       </c>
       <c r="D187" s="19" t="n">
         <v>59.9</v>
       </c>
       <c r="E187" s="20" t="s">
-        <v>1248</v>
+        <v>1254</v>
       </c>
       <c r="F187" s="16" t="s">
         <v>726</v>
@@ -19933,7 +20035,7 @@
         <v>728</v>
       </c>
       <c r="J187" s="18" t="s">
-        <v>1249</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19944,13 +20046,13 @@
         <v>13</v>
       </c>
       <c r="C188" s="18" t="s">
-        <v>1250</v>
+        <v>1256</v>
       </c>
       <c r="D188" s="19" t="n">
         <v>59.9</v>
       </c>
       <c r="E188" s="20" t="s">
-        <v>1251</v>
+        <v>1257</v>
       </c>
       <c r="F188" s="16" t="s">
         <v>726</v>
@@ -19965,7 +20067,7 @@
         <v>728</v>
       </c>
       <c r="J188" s="18" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19976,13 +20078,13 @@
         <v>13</v>
       </c>
       <c r="C189" s="18" t="s">
-        <v>1253</v>
+        <v>1259</v>
       </c>
       <c r="D189" s="19" t="n">
         <v>54.9</v>
       </c>
       <c r="E189" s="20" t="s">
-        <v>1254</v>
+        <v>1260</v>
       </c>
       <c r="F189" s="16" t="s">
         <v>726</v>
@@ -19997,7 +20099,7 @@
         <v>728</v>
       </c>
       <c r="J189" s="18" t="s">
-        <v>1255</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20008,13 +20110,13 @@
         <v>13</v>
       </c>
       <c r="C190" s="18" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="D190" s="19" t="n">
         <v>59.9</v>
       </c>
       <c r="E190" s="20" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="F190" s="16" t="s">
         <v>726</v>
@@ -20029,7 +20131,7 @@
         <v>728</v>
       </c>
       <c r="J190" s="18" t="s">
-        <v>1258</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20040,13 +20142,13 @@
         <v>13</v>
       </c>
       <c r="C191" s="18" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="D191" s="19" t="n">
         <v>49.9</v>
       </c>
       <c r="E191" s="20" t="s">
-        <v>1260</v>
+        <v>1266</v>
       </c>
       <c r="F191" s="16" t="s">
         <v>726</v>
@@ -20061,7 +20163,7 @@
         <v>728</v>
       </c>
       <c r="J191" s="18" t="s">
-        <v>1261</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20072,13 +20174,13 @@
         <v>13</v>
       </c>
       <c r="C192" s="18" t="s">
-        <v>1262</v>
+        <v>1268</v>
       </c>
       <c r="D192" s="19" t="n">
         <v>59.9</v>
       </c>
       <c r="E192" s="20" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="F192" s="16" t="s">
         <v>726</v>
@@ -20093,7 +20195,7 @@
         <v>728</v>
       </c>
       <c r="J192" s="18" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20104,13 +20206,13 @@
         <v>13</v>
       </c>
       <c r="C193" s="18" t="s">
-        <v>1265</v>
+        <v>1271</v>
       </c>
       <c r="D193" s="19" t="n">
         <v>49.9</v>
       </c>
       <c r="E193" s="20" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="F193" s="16" t="s">
         <v>726</v>
@@ -20125,7 +20227,7 @@
         <v>728</v>
       </c>
       <c r="J193" s="18" t="s">
-        <v>1267</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20136,13 +20238,13 @@
         <v>13</v>
       </c>
       <c r="C194" s="18" t="s">
-        <v>1268</v>
+        <v>1274</v>
       </c>
       <c r="D194" s="19" t="n">
         <v>49.9</v>
       </c>
       <c r="E194" s="20" t="s">
-        <v>1269</v>
+        <v>1275</v>
       </c>
       <c r="F194" s="16" t="s">
         <v>726</v>
@@ -20157,7 +20259,7 @@
         <v>728</v>
       </c>
       <c r="J194" s="18" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20168,13 +20270,13 @@
         <v>13</v>
       </c>
       <c r="C195" s="18" t="s">
-        <v>1271</v>
+        <v>1277</v>
       </c>
       <c r="D195" s="19" t="n">
         <v>49.9</v>
       </c>
       <c r="E195" s="20" t="s">
-        <v>1272</v>
+        <v>1278</v>
       </c>
       <c r="F195" s="16" t="s">
         <v>726</v>
@@ -20189,7 +20291,7 @@
         <v>728</v>
       </c>
       <c r="J195" s="18" t="s">
-        <v>1273</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20200,13 +20302,13 @@
         <v>13</v>
       </c>
       <c r="C196" s="18" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="D196" s="19" t="n">
         <v>49.9</v>
       </c>
       <c r="E196" s="20" t="s">
-        <v>1275</v>
+        <v>1281</v>
       </c>
       <c r="F196" s="16" t="s">
         <v>726</v>
@@ -20221,7 +20323,7 @@
         <v>728</v>
       </c>
       <c r="J196" s="18" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20232,13 +20334,13 @@
         <v>14</v>
       </c>
       <c r="C197" s="18" t="s">
-        <v>1277</v>
+        <v>1283</v>
       </c>
       <c r="D197" s="19" t="n">
         <v>59.9</v>
       </c>
       <c r="E197" s="20" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
       <c r="F197" s="16" t="s">
         <v>726</v>
@@ -20253,10 +20355,10 @@
         <v>728</v>
       </c>
       <c r="J197" s="18" t="s">
-        <v>1279</v>
-      </c>
-    </row>
-    <row r="198" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="16" t="n">
         <v>197</v>
       </c>
@@ -20264,31 +20366,31 @@
         <v>14</v>
       </c>
       <c r="C198" s="18" t="s">
-        <v>1280</v>
+        <v>1286</v>
       </c>
       <c r="D198" s="19" t="n">
-        <v>59.9</v>
+        <v>49</v>
       </c>
       <c r="E198" s="20" t="s">
-        <v>1281</v>
+        <v>1287</v>
       </c>
       <c r="F198" s="16" t="s">
-        <v>726</v>
+        <v>784</v>
       </c>
       <c r="G198" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H198" s="18" t="s">
-        <v>768</v>
+        <v>785</v>
       </c>
       <c r="I198" s="18" t="s">
-        <v>728</v>
+        <v>786</v>
       </c>
       <c r="J198" s="18" t="s">
-        <v>1282</v>
-      </c>
-    </row>
-    <row r="199" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="16" t="n">
         <v>198</v>
       </c>
@@ -20296,31 +20398,31 @@
         <v>14</v>
       </c>
       <c r="C199" s="18" t="s">
-        <v>1283</v>
+        <v>1289</v>
       </c>
       <c r="D199" s="19" t="n">
-        <v>59.9</v>
+        <v>59</v>
       </c>
       <c r="E199" s="20" t="s">
-        <v>1284</v>
+        <v>1290</v>
       </c>
       <c r="F199" s="16" t="s">
-        <v>726</v>
+        <v>772</v>
       </c>
       <c r="G199" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H199" s="18" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="I199" s="18" t="s">
-        <v>728</v>
+        <v>774</v>
       </c>
       <c r="J199" s="18" t="s">
-        <v>1285</v>
-      </c>
-    </row>
-    <row r="200" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="16" t="n">
         <v>199</v>
       </c>
@@ -20328,31 +20430,31 @@
         <v>14</v>
       </c>
       <c r="C200" s="18" t="s">
-        <v>1286</v>
+        <v>1292</v>
       </c>
       <c r="D200" s="19" t="n">
-        <v>45</v>
+        <v>59.9</v>
       </c>
       <c r="E200" s="20" t="s">
-        <v>1287</v>
+        <v>1293</v>
       </c>
       <c r="F200" s="16" t="s">
-        <v>784</v>
+        <v>726</v>
       </c>
       <c r="G200" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H200" s="18" t="s">
-        <v>785</v>
+        <v>768</v>
       </c>
       <c r="I200" s="18" t="s">
-        <v>786</v>
+        <v>728</v>
       </c>
       <c r="J200" s="18" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="201" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="16" t="n">
         <v>200</v>
       </c>
@@ -20360,28 +20462,28 @@
         <v>14</v>
       </c>
       <c r="C201" s="18" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
       <c r="D201" s="19" t="n">
-        <v>45</v>
+        <v>59.9</v>
       </c>
       <c r="E201" s="20" t="s">
-        <v>1290</v>
+        <v>1296</v>
       </c>
       <c r="F201" s="16" t="s">
-        <v>784</v>
+        <v>726</v>
       </c>
       <c r="G201" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H201" s="18" t="s">
-        <v>785</v>
+        <v>768</v>
       </c>
       <c r="I201" s="18" t="s">
-        <v>786</v>
+        <v>728</v>
       </c>
       <c r="J201" s="18" t="s">
-        <v>1291</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20392,31 +20494,31 @@
         <v>14</v>
       </c>
       <c r="C202" s="18" t="s">
-        <v>1292</v>
+        <v>1298</v>
       </c>
       <c r="D202" s="19" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
       <c r="E202" s="20" t="s">
-        <v>1293</v>
+        <v>1299</v>
       </c>
       <c r="F202" s="16" t="s">
-        <v>1294</v>
+        <v>726</v>
       </c>
       <c r="G202" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H202" s="18" t="s">
-        <v>163</v>
+        <v>768</v>
       </c>
       <c r="I202" s="18" t="s">
-        <v>1295</v>
+        <v>728</v>
       </c>
       <c r="J202" s="18" t="s">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="203" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="16" t="n">
         <v>202</v>
       </c>
@@ -20424,31 +20526,31 @@
         <v>14</v>
       </c>
       <c r="C203" s="18" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
       <c r="D203" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E203" s="20" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
       <c r="F203" s="16" t="s">
-        <v>1294</v>
+        <v>784</v>
       </c>
       <c r="G203" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H203" s="18" t="s">
-        <v>163</v>
+        <v>785</v>
       </c>
       <c r="I203" s="18" t="s">
-        <v>1299</v>
+        <v>786</v>
       </c>
       <c r="J203" s="18" t="s">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="204" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="16" t="n">
         <v>203</v>
       </c>
@@ -20456,28 +20558,28 @@
         <v>14</v>
       </c>
       <c r="C204" s="18" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="D204" s="19" t="n">
-        <v>59.9</v>
+        <v>45</v>
       </c>
       <c r="E204" s="20" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="F204" s="16" t="s">
-        <v>726</v>
+        <v>784</v>
       </c>
       <c r="G204" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H204" s="18" t="s">
-        <v>768</v>
+        <v>785</v>
       </c>
       <c r="I204" s="18" t="s">
-        <v>728</v>
+        <v>786</v>
       </c>
       <c r="J204" s="18" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20488,28 +20590,28 @@
         <v>14</v>
       </c>
       <c r="C205" s="18" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="D205" s="19" t="n">
-        <v>59.9</v>
+        <v>60</v>
       </c>
       <c r="E205" s="20" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="F205" s="16" t="s">
-        <v>726</v>
+        <v>1309</v>
       </c>
       <c r="G205" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H205" s="18" t="s">
-        <v>768</v>
+        <v>163</v>
       </c>
       <c r="I205" s="18" t="s">
-        <v>728</v>
+        <v>1310</v>
       </c>
       <c r="J205" s="18" t="s">
-        <v>1306</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20520,28 +20622,28 @@
         <v>14</v>
       </c>
       <c r="C206" s="18" t="s">
-        <v>1307</v>
+        <v>1312</v>
       </c>
       <c r="D206" s="19" t="n">
-        <v>59.9</v>
+        <v>45</v>
       </c>
       <c r="E206" s="20" t="s">
-        <v>1308</v>
+        <v>1313</v>
       </c>
       <c r="F206" s="16" t="s">
-        <v>726</v>
+        <v>1309</v>
       </c>
       <c r="G206" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H206" s="18" t="s">
-        <v>768</v>
+        <v>163</v>
       </c>
       <c r="I206" s="18" t="s">
-        <v>728</v>
+        <v>1314</v>
       </c>
       <c r="J206" s="18" t="s">
-        <v>1309</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20552,13 +20654,13 @@
         <v>14</v>
       </c>
       <c r="C207" s="18" t="s">
-        <v>1310</v>
+        <v>1316</v>
       </c>
       <c r="D207" s="19" t="n">
         <v>59.9</v>
       </c>
       <c r="E207" s="20" t="s">
-        <v>1311</v>
+        <v>1317</v>
       </c>
       <c r="F207" s="16" t="s">
         <v>726</v>
@@ -20573,7 +20675,7 @@
         <v>728</v>
       </c>
       <c r="J207" s="18" t="s">
-        <v>1312</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20584,13 +20686,13 @@
         <v>14</v>
       </c>
       <c r="C208" s="18" t="s">
-        <v>1313</v>
+        <v>1319</v>
       </c>
       <c r="D208" s="19" t="n">
         <v>59.9</v>
       </c>
       <c r="E208" s="20" t="s">
-        <v>1314</v>
+        <v>1320</v>
       </c>
       <c r="F208" s="16" t="s">
         <v>726</v>
@@ -20605,7 +20707,7 @@
         <v>728</v>
       </c>
       <c r="J208" s="18" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20616,13 +20718,13 @@
         <v>14</v>
       </c>
       <c r="C209" s="18" t="s">
-        <v>1316</v>
+        <v>1322</v>
       </c>
       <c r="D209" s="19" t="n">
         <v>59.9</v>
       </c>
       <c r="E209" s="20" t="s">
-        <v>1317</v>
+        <v>1323</v>
       </c>
       <c r="F209" s="16" t="s">
         <v>726</v>
@@ -20637,7 +20739,7 @@
         <v>728</v>
       </c>
       <c r="J209" s="18" t="s">
-        <v>1318</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20648,13 +20750,13 @@
         <v>14</v>
       </c>
       <c r="C210" s="18" t="s">
-        <v>1319</v>
+        <v>1325</v>
       </c>
       <c r="D210" s="19" t="n">
         <v>59.9</v>
       </c>
       <c r="E210" s="20" t="s">
-        <v>1320</v>
+        <v>1326</v>
       </c>
       <c r="F210" s="16" t="s">
         <v>726</v>
@@ -20669,7 +20771,7 @@
         <v>728</v>
       </c>
       <c r="J210" s="18" t="s">
-        <v>1321</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20680,13 +20782,13 @@
         <v>14</v>
       </c>
       <c r="C211" s="18" t="s">
-        <v>1322</v>
+        <v>1328</v>
       </c>
       <c r="D211" s="19" t="n">
         <v>59.9</v>
       </c>
       <c r="E211" s="20" t="s">
-        <v>1323</v>
+        <v>1329</v>
       </c>
       <c r="F211" s="16" t="s">
         <v>726</v>
@@ -20701,7 +20803,7 @@
         <v>728</v>
       </c>
       <c r="J211" s="18" t="s">
-        <v>1324</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20712,13 +20814,13 @@
         <v>14</v>
       </c>
       <c r="C212" s="18" t="s">
-        <v>1325</v>
+        <v>1331</v>
       </c>
       <c r="D212" s="19" t="n">
         <v>59.9</v>
       </c>
       <c r="E212" s="20" t="s">
-        <v>1326</v>
+        <v>1332</v>
       </c>
       <c r="F212" s="16" t="s">
         <v>726</v>
@@ -20733,7 +20835,7 @@
         <v>728</v>
       </c>
       <c r="J212" s="18" t="s">
-        <v>1327</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20744,13 +20846,13 @@
         <v>14</v>
       </c>
       <c r="C213" s="18" t="s">
-        <v>1328</v>
+        <v>1334</v>
       </c>
       <c r="D213" s="19" t="n">
         <v>59.9</v>
       </c>
       <c r="E213" s="20" t="s">
-        <v>1329</v>
+        <v>1335</v>
       </c>
       <c r="F213" s="16" t="s">
         <v>726</v>
@@ -20765,7 +20867,7 @@
         <v>728</v>
       </c>
       <c r="J213" s="18" t="s">
-        <v>1330</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20776,13 +20878,13 @@
         <v>14</v>
       </c>
       <c r="C214" s="18" t="s">
-        <v>1331</v>
+        <v>1337</v>
       </c>
       <c r="D214" s="19" t="n">
         <v>59.9</v>
       </c>
       <c r="E214" s="20" t="s">
-        <v>1332</v>
+        <v>1338</v>
       </c>
       <c r="F214" s="16" t="s">
         <v>726</v>
@@ -20797,7 +20899,7 @@
         <v>728</v>
       </c>
       <c r="J214" s="18" t="s">
-        <v>1333</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20808,13 +20910,13 @@
         <v>14</v>
       </c>
       <c r="C215" s="18" t="s">
-        <v>1334</v>
+        <v>1340</v>
       </c>
       <c r="D215" s="19" t="n">
         <v>59.9</v>
       </c>
       <c r="E215" s="20" t="s">
-        <v>1335</v>
+        <v>1341</v>
       </c>
       <c r="F215" s="16" t="s">
         <v>726</v>
@@ -20829,10 +20931,10 @@
         <v>728</v>
       </c>
       <c r="J215" s="18" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="216" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="16" t="n">
         <v>215</v>
       </c>
@@ -20840,31 +20942,31 @@
         <v>14</v>
       </c>
       <c r="C216" s="18" t="s">
-        <v>1337</v>
+        <v>1343</v>
       </c>
       <c r="D216" s="19" t="n">
-        <v>59</v>
+        <v>59.9</v>
       </c>
       <c r="E216" s="20" t="s">
-        <v>1338</v>
+        <v>1344</v>
       </c>
       <c r="F216" s="16" t="s">
-        <v>772</v>
+        <v>726</v>
       </c>
       <c r="G216" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H216" s="18" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="I216" s="18" t="s">
-        <v>774</v>
+        <v>728</v>
       </c>
       <c r="J216" s="18" t="s">
-        <v>1339</v>
-      </c>
-    </row>
-    <row r="217" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="16" t="n">
         <v>216</v>
       </c>
@@ -20872,31 +20974,31 @@
         <v>14</v>
       </c>
       <c r="C217" s="18" t="s">
-        <v>1340</v>
+        <v>1346</v>
       </c>
       <c r="D217" s="19" t="n">
-        <v>45</v>
+        <v>59.9</v>
       </c>
       <c r="E217" s="20" t="s">
-        <v>1341</v>
+        <v>1347</v>
       </c>
       <c r="F217" s="16" t="s">
-        <v>772</v>
+        <v>726</v>
       </c>
       <c r="G217" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H217" s="18" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="I217" s="18" t="s">
-        <v>774</v>
+        <v>728</v>
       </c>
       <c r="J217" s="18" t="s">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="218" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="16" t="n">
         <v>217</v>
       </c>
@@ -20904,28 +21006,28 @@
         <v>14</v>
       </c>
       <c r="C218" s="18" t="s">
-        <v>1343</v>
+        <v>1349</v>
       </c>
       <c r="D218" s="19" t="n">
-        <v>59</v>
+        <v>59.9</v>
       </c>
       <c r="E218" s="20" t="s">
-        <v>1344</v>
+        <v>1350</v>
       </c>
       <c r="F218" s="16" t="s">
-        <v>772</v>
+        <v>726</v>
       </c>
       <c r="G218" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H218" s="18" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="I218" s="18" t="s">
-        <v>774</v>
+        <v>728</v>
       </c>
       <c r="J218" s="18" t="s">
-        <v>1345</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20936,28 +21038,28 @@
         <v>14</v>
       </c>
       <c r="C219" s="18" t="s">
-        <v>1346</v>
+        <v>1352</v>
       </c>
       <c r="D219" s="19" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E219" s="20" t="s">
-        <v>1347</v>
+        <v>1353</v>
       </c>
       <c r="F219" s="16" t="s">
-        <v>772</v>
+        <v>793</v>
       </c>
       <c r="G219" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H219" s="18" t="s">
-        <v>773</v>
+        <v>794</v>
       </c>
       <c r="I219" s="18" t="s">
-        <v>774</v>
+        <v>1354</v>
       </c>
       <c r="J219" s="18" t="s">
-        <v>1348</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20968,13 +21070,13 @@
         <v>14</v>
       </c>
       <c r="C220" s="18" t="s">
-        <v>1349</v>
+        <v>1356</v>
       </c>
       <c r="D220" s="19" t="n">
         <v>59</v>
       </c>
       <c r="E220" s="20" t="s">
-        <v>1350</v>
+        <v>1357</v>
       </c>
       <c r="F220" s="16" t="s">
         <v>772</v>
@@ -20989,7 +21091,7 @@
         <v>774</v>
       </c>
       <c r="J220" s="18" t="s">
-        <v>1351</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21000,13 +21102,13 @@
         <v>14</v>
       </c>
       <c r="C221" s="18" t="s">
-        <v>1352</v>
+        <v>1359</v>
       </c>
       <c r="D221" s="19" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E221" s="20" t="s">
-        <v>1353</v>
+        <v>1360</v>
       </c>
       <c r="F221" s="16" t="s">
         <v>772</v>
@@ -21021,10 +21123,10 @@
         <v>774</v>
       </c>
       <c r="J221" s="18" t="s">
-        <v>1354</v>
-      </c>
-    </row>
-    <row r="222" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="16" t="n">
         <v>221</v>
       </c>
@@ -21032,31 +21134,31 @@
         <v>14</v>
       </c>
       <c r="C222" s="18" t="s">
-        <v>1355</v>
+        <v>1362</v>
       </c>
       <c r="D222" s="19" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E222" s="20" t="s">
-        <v>1356</v>
+        <v>1363</v>
       </c>
       <c r="F222" s="16" t="s">
-        <v>1294</v>
+        <v>772</v>
       </c>
       <c r="G222" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H222" s="18" t="s">
-        <v>163</v>
+        <v>773</v>
       </c>
       <c r="I222" s="18" t="s">
-        <v>1299</v>
+        <v>774</v>
       </c>
       <c r="J222" s="18" t="s">
-        <v>1357</v>
-      </c>
-    </row>
-    <row r="223" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="16" t="n">
         <v>222</v>
       </c>
@@ -21064,31 +21166,31 @@
         <v>14</v>
       </c>
       <c r="C223" s="18" t="s">
-        <v>1358</v>
+        <v>1365</v>
       </c>
       <c r="D223" s="19" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E223" s="20" t="s">
-        <v>1359</v>
+        <v>1366</v>
       </c>
       <c r="F223" s="16" t="s">
-        <v>1294</v>
+        <v>772</v>
       </c>
       <c r="G223" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H223" s="18" t="s">
-        <v>163</v>
+        <v>773</v>
       </c>
       <c r="I223" s="18" t="s">
-        <v>1360</v>
+        <v>774</v>
       </c>
       <c r="J223" s="18" t="s">
-        <v>1361</v>
-      </c>
-    </row>
-    <row r="224" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="16" t="n">
         <v>223</v>
       </c>
@@ -21096,31 +21198,31 @@
         <v>14</v>
       </c>
       <c r="C224" s="18" t="s">
-        <v>1362</v>
+        <v>1368</v>
       </c>
       <c r="D224" s="19" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="E224" s="20" t="s">
-        <v>1363</v>
+        <v>1369</v>
       </c>
       <c r="F224" s="16" t="s">
-        <v>1294</v>
+        <v>772</v>
       </c>
       <c r="G224" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H224" s="18" t="s">
-        <v>163</v>
+        <v>773</v>
       </c>
       <c r="I224" s="18" t="s">
-        <v>1299</v>
+        <v>774</v>
       </c>
       <c r="J224" s="18" t="s">
-        <v>1364</v>
-      </c>
-    </row>
-    <row r="225" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="16" t="n">
         <v>224</v>
       </c>
@@ -21128,28 +21230,28 @@
         <v>14</v>
       </c>
       <c r="C225" s="18" t="s">
-        <v>1365</v>
+        <v>1371</v>
       </c>
       <c r="D225" s="19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E225" s="20" t="s">
-        <v>1366</v>
+        <v>1372</v>
       </c>
       <c r="F225" s="16" t="s">
-        <v>1294</v>
+        <v>772</v>
       </c>
       <c r="G225" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H225" s="18" t="s">
-        <v>163</v>
+        <v>773</v>
       </c>
       <c r="I225" s="18" t="s">
-        <v>1299</v>
+        <v>774</v>
       </c>
       <c r="J225" s="18" t="s">
-        <v>1367</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21160,16 +21262,16 @@
         <v>14</v>
       </c>
       <c r="C226" s="18" t="s">
-        <v>1368</v>
+        <v>1374</v>
       </c>
       <c r="D226" s="19" t="n">
-        <v>47.6</v>
+        <v>60</v>
       </c>
       <c r="E226" s="20" t="s">
-        <v>1369</v>
+        <v>1375</v>
       </c>
       <c r="F226" s="16" t="s">
-        <v>1294</v>
+        <v>1309</v>
       </c>
       <c r="G226" s="16" t="s">
         <v>38</v>
@@ -21178,10 +21280,10 @@
         <v>163</v>
       </c>
       <c r="I226" s="18" t="s">
-        <v>1299</v>
+        <v>1314</v>
       </c>
       <c r="J226" s="18" t="s">
-        <v>1370</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21192,16 +21294,16 @@
         <v>14</v>
       </c>
       <c r="C227" s="18" t="s">
-        <v>1371</v>
+        <v>1377</v>
       </c>
       <c r="D227" s="19" t="n">
-        <v>47.6</v>
+        <v>55</v>
       </c>
       <c r="E227" s="20" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="F227" s="16" t="s">
-        <v>1294</v>
+        <v>1309</v>
       </c>
       <c r="G227" s="16" t="s">
         <v>38</v>
@@ -21210,10 +21312,10 @@
         <v>163</v>
       </c>
       <c r="I227" s="18" t="s">
-        <v>1299</v>
+        <v>1379</v>
       </c>
       <c r="J227" s="18" t="s">
-        <v>1373</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21224,16 +21326,16 @@
         <v>14</v>
       </c>
       <c r="C228" s="18" t="s">
-        <v>1374</v>
+        <v>1381</v>
       </c>
       <c r="D228" s="19" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E228" s="20" t="s">
-        <v>1375</v>
+        <v>1382</v>
       </c>
       <c r="F228" s="16" t="s">
-        <v>1294</v>
+        <v>1309</v>
       </c>
       <c r="G228" s="16" t="s">
         <v>38</v>
@@ -21242,13 +21344,13 @@
         <v>163</v>
       </c>
       <c r="I228" s="18" t="s">
-        <v>1299</v>
+        <v>1314</v>
       </c>
       <c r="J228" s="18" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="229" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="16" t="n">
         <v>228</v>
       </c>
@@ -21256,31 +21358,31 @@
         <v>14</v>
       </c>
       <c r="C229" s="18" t="s">
-        <v>1377</v>
+        <v>1384</v>
       </c>
       <c r="D229" s="19" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E229" s="20" t="s">
-        <v>1378</v>
+        <v>1385</v>
       </c>
       <c r="F229" s="16" t="s">
-        <v>784</v>
+        <v>1309</v>
       </c>
       <c r="G229" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H229" s="18" t="s">
-        <v>785</v>
+        <v>163</v>
       </c>
       <c r="I229" s="18" t="s">
-        <v>786</v>
+        <v>1314</v>
       </c>
       <c r="J229" s="18" t="s">
-        <v>1379</v>
-      </c>
-    </row>
-    <row r="230" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="16" t="n">
         <v>229</v>
       </c>
@@ -21288,31 +21390,31 @@
         <v>14</v>
       </c>
       <c r="C230" s="18" t="s">
-        <v>1380</v>
+        <v>1387</v>
       </c>
       <c r="D230" s="19" t="n">
-        <v>45</v>
+        <v>47.6</v>
       </c>
       <c r="E230" s="20" t="s">
-        <v>1381</v>
+        <v>1388</v>
       </c>
       <c r="F230" s="16" t="s">
-        <v>784</v>
+        <v>1309</v>
       </c>
       <c r="G230" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H230" s="18" t="s">
-        <v>785</v>
+        <v>163</v>
       </c>
       <c r="I230" s="18" t="s">
-        <v>786</v>
+        <v>1314</v>
       </c>
       <c r="J230" s="18" t="s">
-        <v>1382</v>
-      </c>
-    </row>
-    <row r="231" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="16" t="n">
         <v>230</v>
       </c>
@@ -21320,31 +21422,31 @@
         <v>14</v>
       </c>
       <c r="C231" s="18" t="s">
-        <v>1383</v>
+        <v>1390</v>
       </c>
       <c r="D231" s="19" t="n">
-        <v>55</v>
+        <v>47.6</v>
       </c>
       <c r="E231" s="20" t="s">
-        <v>1384</v>
+        <v>1391</v>
       </c>
       <c r="F231" s="16" t="s">
-        <v>784</v>
+        <v>1309</v>
       </c>
       <c r="G231" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H231" s="18" t="s">
-        <v>785</v>
+        <v>163</v>
       </c>
       <c r="I231" s="18" t="s">
-        <v>786</v>
+        <v>1314</v>
       </c>
       <c r="J231" s="18" t="s">
-        <v>1385</v>
-      </c>
-    </row>
-    <row r="232" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="16" t="n">
         <v>231</v>
       </c>
@@ -21352,31 +21454,31 @@
         <v>14</v>
       </c>
       <c r="C232" s="18" t="s">
-        <v>1386</v>
+        <v>1393</v>
       </c>
       <c r="D232" s="19" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E232" s="20" t="s">
-        <v>1387</v>
+        <v>1394</v>
       </c>
       <c r="F232" s="16" t="s">
-        <v>784</v>
+        <v>1309</v>
       </c>
       <c r="G232" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H232" s="18" t="s">
-        <v>785</v>
+        <v>163</v>
       </c>
       <c r="I232" s="18" t="s">
-        <v>786</v>
+        <v>1314</v>
       </c>
       <c r="J232" s="18" t="s">
-        <v>1388</v>
-      </c>
-    </row>
-    <row r="233" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="16" t="n">
         <v>232</v>
       </c>
@@ -21384,31 +21486,31 @@
         <v>14</v>
       </c>
       <c r="C233" s="18" t="s">
-        <v>1389</v>
+        <v>1396</v>
       </c>
       <c r="D233" s="19" t="n">
-        <v>49</v>
+        <v>48.5</v>
       </c>
       <c r="E233" s="20" t="s">
-        <v>1390</v>
+        <v>1397</v>
       </c>
       <c r="F233" s="16" t="s">
-        <v>784</v>
+        <v>799</v>
       </c>
       <c r="G233" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H233" s="18" t="s">
-        <v>785</v>
+        <v>800</v>
       </c>
       <c r="I233" s="18" t="s">
-        <v>786</v>
+        <v>801</v>
       </c>
       <c r="J233" s="18" t="s">
-        <v>1391</v>
-      </c>
-    </row>
-    <row r="234" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="16" t="n">
         <v>233</v>
       </c>
@@ -21416,31 +21518,31 @@
         <v>14</v>
       </c>
       <c r="C234" s="18" t="s">
-        <v>1392</v>
+        <v>1399</v>
       </c>
       <c r="D234" s="19" t="n">
-        <v>49</v>
+        <v>46.99</v>
       </c>
       <c r="E234" s="20" t="s">
-        <v>1393</v>
+        <v>1400</v>
       </c>
       <c r="F234" s="16" t="s">
-        <v>784</v>
+        <v>799</v>
       </c>
       <c r="G234" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H234" s="18" t="s">
-        <v>785</v>
+        <v>800</v>
       </c>
       <c r="I234" s="18" t="s">
-        <v>786</v>
+        <v>801</v>
       </c>
       <c r="J234" s="18" t="s">
-        <v>1394</v>
-      </c>
-    </row>
-    <row r="235" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="16" t="n">
         <v>234</v>
       </c>
@@ -21448,31 +21550,31 @@
         <v>14</v>
       </c>
       <c r="C235" s="18" t="s">
-        <v>1395</v>
+        <v>1402</v>
       </c>
       <c r="D235" s="19" t="n">
-        <v>59</v>
+        <v>46.99</v>
       </c>
       <c r="E235" s="20" t="s">
-        <v>1396</v>
+        <v>1403</v>
       </c>
       <c r="F235" s="16" t="s">
-        <v>784</v>
+        <v>799</v>
       </c>
       <c r="G235" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H235" s="18" t="s">
-        <v>785</v>
+        <v>800</v>
       </c>
       <c r="I235" s="18" t="s">
-        <v>786</v>
+        <v>801</v>
       </c>
       <c r="J235" s="18" t="s">
-        <v>1397</v>
-      </c>
-    </row>
-    <row r="236" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="16" t="n">
         <v>235</v>
       </c>
@@ -21480,31 +21582,31 @@
         <v>14</v>
       </c>
       <c r="C236" s="18" t="s">
-        <v>1398</v>
+        <v>1405</v>
       </c>
       <c r="D236" s="19" t="n">
-        <v>45</v>
+        <v>46.99</v>
       </c>
       <c r="E236" s="20" t="s">
-        <v>1399</v>
+        <v>1406</v>
       </c>
       <c r="F236" s="16" t="s">
-        <v>784</v>
+        <v>799</v>
       </c>
       <c r="G236" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H236" s="18" t="s">
-        <v>785</v>
+        <v>800</v>
       </c>
       <c r="I236" s="18" t="s">
-        <v>786</v>
+        <v>801</v>
       </c>
       <c r="J236" s="18" t="s">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="237" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="16" t="n">
         <v>236</v>
       </c>
@@ -21512,28 +21614,28 @@
         <v>14</v>
       </c>
       <c r="C237" s="18" t="s">
-        <v>1401</v>
+        <v>1408</v>
       </c>
       <c r="D237" s="19" t="n">
-        <v>45</v>
+        <v>46.99</v>
       </c>
       <c r="E237" s="20" t="s">
-        <v>1402</v>
+        <v>1409</v>
       </c>
       <c r="F237" s="16" t="s">
-        <v>784</v>
+        <v>799</v>
       </c>
       <c r="G237" s="16" t="s">
         <v>38</v>
       </c>
       <c r="H237" s="18" t="s">
-        <v>785</v>
+        <v>800</v>
       </c>
       <c r="I237" s="18" t="s">
-        <v>786</v>
+        <v>801</v>
       </c>
       <c r="J237" s="18" t="s">
-        <v>1403</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21544,13 +21646,13 @@
         <v>14</v>
       </c>
       <c r="C238" s="18" t="s">
-        <v>1404</v>
+        <v>1411</v>
       </c>
       <c r="D238" s="19" t="n">
         <v>59</v>
       </c>
       <c r="E238" s="20" t="s">
-        <v>1405</v>
+        <v>1412</v>
       </c>
       <c r="F238" s="16" t="s">
         <v>784</v>
@@ -21565,7 +21667,7 @@
         <v>786</v>
       </c>
       <c r="J238" s="18" t="s">
-        <v>1406</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21576,13 +21678,13 @@
         <v>14</v>
       </c>
       <c r="C239" s="18" t="s">
-        <v>1407</v>
+        <v>1414</v>
       </c>
       <c r="D239" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E239" s="20" t="s">
-        <v>1408</v>
+        <v>1415</v>
       </c>
       <c r="F239" s="16" t="s">
         <v>784</v>
@@ -21597,7 +21699,7 @@
         <v>786</v>
       </c>
       <c r="J239" s="18" t="s">
-        <v>1409</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21608,13 +21710,13 @@
         <v>14</v>
       </c>
       <c r="C240" s="18" t="s">
-        <v>1410</v>
+        <v>1417</v>
       </c>
       <c r="D240" s="19" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E240" s="20" t="s">
-        <v>1411</v>
+        <v>1418</v>
       </c>
       <c r="F240" s="16" t="s">
         <v>784</v>
@@ -21629,7 +21731,7 @@
         <v>786</v>
       </c>
       <c r="J240" s="18" t="s">
-        <v>1412</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21640,13 +21742,13 @@
         <v>14</v>
       </c>
       <c r="C241" s="18" t="s">
-        <v>1413</v>
+        <v>1420</v>
       </c>
       <c r="D241" s="19" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E241" s="20" t="s">
-        <v>1414</v>
+        <v>1421</v>
       </c>
       <c r="F241" s="16" t="s">
         <v>784</v>
@@ -21661,10 +21763,10 @@
         <v>786</v>
       </c>
       <c r="J241" s="18" t="s">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="242" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="16" t="n">
         <v>241</v>
       </c>
@@ -21672,13 +21774,13 @@
         <v>14</v>
       </c>
       <c r="C242" s="18" t="s">
-        <v>1416</v>
+        <v>1423</v>
       </c>
       <c r="D242" s="19" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E242" s="20" t="s">
-        <v>1417</v>
+        <v>1424</v>
       </c>
       <c r="F242" s="16" t="s">
         <v>784</v>
@@ -21693,7 +21795,7 @@
         <v>786</v>
       </c>
       <c r="J242" s="18" t="s">
-        <v>1418</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21704,13 +21806,13 @@
         <v>14</v>
       </c>
       <c r="C243" s="18" t="s">
-        <v>1419</v>
+        <v>1426</v>
       </c>
       <c r="D243" s="19" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E243" s="20" t="s">
-        <v>1420</v>
+        <v>1427</v>
       </c>
       <c r="F243" s="16" t="s">
         <v>784</v>
@@ -21725,7 +21827,7 @@
         <v>786</v>
       </c>
       <c r="J243" s="18" t="s">
-        <v>1421</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21736,13 +21838,13 @@
         <v>14</v>
       </c>
       <c r="C244" s="18" t="s">
-        <v>1422</v>
+        <v>1429</v>
       </c>
       <c r="D244" s="19" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E244" s="20" t="s">
-        <v>1423</v>
+        <v>1430</v>
       </c>
       <c r="F244" s="16" t="s">
         <v>784</v>
@@ -21757,7 +21859,7 @@
         <v>786</v>
       </c>
       <c r="J244" s="18" t="s">
-        <v>1424</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21768,13 +21870,13 @@
         <v>14</v>
       </c>
       <c r="C245" s="18" t="s">
-        <v>1425</v>
+        <v>1432</v>
       </c>
       <c r="D245" s="19" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E245" s="20" t="s">
-        <v>1426</v>
+        <v>1433</v>
       </c>
       <c r="F245" s="16" t="s">
         <v>784</v>
@@ -21789,7 +21891,7 @@
         <v>786</v>
       </c>
       <c r="J245" s="18" t="s">
-        <v>1427</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21800,13 +21902,13 @@
         <v>14</v>
       </c>
       <c r="C246" s="18" t="s">
-        <v>1428</v>
+        <v>1435</v>
       </c>
       <c r="D246" s="19" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E246" s="20" t="s">
-        <v>1429</v>
+        <v>1436</v>
       </c>
       <c r="F246" s="16" t="s">
         <v>784</v>
@@ -21821,7 +21923,7 @@
         <v>786</v>
       </c>
       <c r="J246" s="18" t="s">
-        <v>1430</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21832,13 +21934,13 @@
         <v>14</v>
       </c>
       <c r="C247" s="18" t="s">
-        <v>1431</v>
+        <v>1438</v>
       </c>
       <c r="D247" s="19" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E247" s="20" t="s">
-        <v>1432</v>
+        <v>1439</v>
       </c>
       <c r="F247" s="16" t="s">
         <v>784</v>
@@ -21853,7 +21955,7 @@
         <v>786</v>
       </c>
       <c r="J247" s="18" t="s">
-        <v>1433</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21864,13 +21966,13 @@
         <v>14</v>
       </c>
       <c r="C248" s="18" t="s">
-        <v>1434</v>
+        <v>1441</v>
       </c>
       <c r="D248" s="19" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E248" s="20" t="s">
-        <v>1435</v>
+        <v>1442</v>
       </c>
       <c r="F248" s="16" t="s">
         <v>784</v>
@@ -21885,10 +21987,10 @@
         <v>786</v>
       </c>
       <c r="J248" s="18" t="s">
-        <v>1436</v>
-      </c>
-    </row>
-    <row r="249" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="16" t="n">
         <v>248</v>
       </c>
@@ -21896,28 +21998,316 @@
         <v>14</v>
       </c>
       <c r="C249" s="18" t="s">
-        <v>1437</v>
+        <v>1444</v>
       </c>
       <c r="D249" s="19" t="n">
+        <v>59</v>
+      </c>
+      <c r="E249" s="20" t="s">
+        <v>1445</v>
+      </c>
+      <c r="F249" s="16" t="s">
+        <v>784</v>
+      </c>
+      <c r="G249" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H249" s="18" t="s">
+        <v>785</v>
+      </c>
+      <c r="I249" s="18" t="s">
+        <v>786</v>
+      </c>
+      <c r="J249" s="18" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="16" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C250" s="18" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D250" s="19" t="n">
+        <v>45</v>
+      </c>
+      <c r="E250" s="20" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F250" s="16" t="s">
+        <v>784</v>
+      </c>
+      <c r="G250" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H250" s="18" t="s">
+        <v>785</v>
+      </c>
+      <c r="I250" s="18" t="s">
+        <v>786</v>
+      </c>
+      <c r="J250" s="18" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C251" s="18" t="s">
+        <v>1450</v>
+      </c>
+      <c r="D251" s="19" t="n">
+        <v>59</v>
+      </c>
+      <c r="E251" s="20" t="s">
+        <v>1451</v>
+      </c>
+      <c r="F251" s="16" t="s">
+        <v>784</v>
+      </c>
+      <c r="G251" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H251" s="18" t="s">
+        <v>785</v>
+      </c>
+      <c r="I251" s="18" t="s">
+        <v>786</v>
+      </c>
+      <c r="J251" s="18" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="252" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="16" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C252" s="18" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D252" s="19" t="n">
+        <v>55</v>
+      </c>
+      <c r="E252" s="20" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F252" s="16" t="s">
+        <v>784</v>
+      </c>
+      <c r="G252" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H252" s="18" t="s">
+        <v>785</v>
+      </c>
+      <c r="I252" s="18" t="s">
+        <v>786</v>
+      </c>
+      <c r="J252" s="18" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="253" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="16" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C253" s="18" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D253" s="19" t="n">
+        <v>45</v>
+      </c>
+      <c r="E253" s="20" t="s">
+        <v>1457</v>
+      </c>
+      <c r="F253" s="16" t="s">
+        <v>784</v>
+      </c>
+      <c r="G253" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H253" s="18" t="s">
+        <v>785</v>
+      </c>
+      <c r="I253" s="18" t="s">
+        <v>786</v>
+      </c>
+      <c r="J253" s="18" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="254" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="16" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C254" s="18" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D254" s="19" t="n">
+        <v>55</v>
+      </c>
+      <c r="E254" s="20" t="s">
+        <v>1460</v>
+      </c>
+      <c r="F254" s="16" t="s">
+        <v>784</v>
+      </c>
+      <c r="G254" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H254" s="18" t="s">
+        <v>785</v>
+      </c>
+      <c r="I254" s="18" t="s">
+        <v>786</v>
+      </c>
+      <c r="J254" s="18" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="255" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="16" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C255" s="18" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D255" s="19" t="n">
+        <v>59</v>
+      </c>
+      <c r="E255" s="20" t="s">
+        <v>1463</v>
+      </c>
+      <c r="F255" s="16" t="s">
+        <v>784</v>
+      </c>
+      <c r="G255" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H255" s="18" t="s">
+        <v>785</v>
+      </c>
+      <c r="I255" s="18" t="s">
+        <v>786</v>
+      </c>
+      <c r="J255" s="18" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="256" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A256" s="16" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C256" s="18" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D256" s="19" t="n">
+        <v>55</v>
+      </c>
+      <c r="E256" s="20" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F256" s="16" t="s">
+        <v>784</v>
+      </c>
+      <c r="G256" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H256" s="18" t="s">
+        <v>785</v>
+      </c>
+      <c r="I256" s="18" t="s">
+        <v>786</v>
+      </c>
+      <c r="J256" s="18" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="16" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C257" s="18" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D257" s="19" t="n">
+        <v>55</v>
+      </c>
+      <c r="E257" s="20" t="s">
+        <v>1469</v>
+      </c>
+      <c r="F257" s="16" t="s">
+        <v>784</v>
+      </c>
+      <c r="G257" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H257" s="18" t="s">
+        <v>785</v>
+      </c>
+      <c r="I257" s="18" t="s">
+        <v>786</v>
+      </c>
+      <c r="J257" s="18" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="16" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C258" s="18" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D258" s="19" t="n">
         <v>60</v>
       </c>
-      <c r="E249" s="20" t="s">
-        <v>1438</v>
-      </c>
-      <c r="F249" s="16" t="s">
-        <v>1294</v>
-      </c>
-      <c r="G249" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="H249" s="18" t="s">
-        <v>1439</v>
-      </c>
-      <c r="I249" s="18" t="s">
-        <v>1440</v>
-      </c>
-      <c r="J249" s="18" t="s">
-        <v>1441</v>
+      <c r="E258" s="20" t="s">
+        <v>1472</v>
+      </c>
+      <c r="F258" s="16" t="s">
+        <v>1309</v>
+      </c>
+      <c r="G258" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H258" s="18" t="s">
+        <v>1473</v>
+      </c>
+      <c r="I258" s="18" t="s">
+        <v>1474</v>
+      </c>
+      <c r="J258" s="18" t="s">
+        <v>1475</v>
       </c>
     </row>
   </sheetData>
@@ -22117,59 +22507,68 @@
     <hyperlink ref="E194" r:id="rId193" display="https://www.bookxcess.com/products/bxosbd-last-rites-9781538775417"/>
     <hyperlink ref="E195" r:id="rId194" display="https://www.bookxcess.com/products/love-and-let-die-9781639363308"/>
     <hyperlink ref="E196" r:id="rId195" display="https://www.bookxcess.com/products/bbw-wh-34947-the-woman-in-me-9781668009048"/>
-    <hyperlink ref="E197" r:id="rId196" display="https://www.bookxcess.com/products/frank-sinatra-pop-art-10x10-287504"/>
-    <hyperlink ref="E198" r:id="rId197" display="https://www.bookxcess.com/products/dua-lipa_we-were-pop-art-10x10-287983"/>
-    <hyperlink ref="E199" r:id="rId198" display="https://www.bookxcess.com/products/paul-stanley-kiss-pop-art-10x10-287461"/>
-    <hyperlink ref="E200" r:id="rId199" display="https://xduniverse.com.my/products/twice-this-is-for-world-tour-in-japan-official-goods-random-trading-card"/>
-    <hyperlink ref="E201" r:id="rId200" display="https://xduniverse.com.my/products/stray-kids-6th-fanmeeting-stay-in-our-little-house-official-merch-special-trading-card"/>
-    <hyperlink ref="E202" r:id="rId201" display="https://tandangstore.com/products/-mitski-the-land-is-inhospitable-and-so-are-we-cassette-coming-soon-"/>
-    <hyperlink ref="E203" r:id="rId202" display="https://tandangstore.com/products/-new-arrival-godflesh-songs-of-love-and-hate-cassette-1"/>
-    <hyperlink ref="E204" r:id="rId203" display="https://www.bookxcess.com/products/armin-van-buuren-pop-art-10x10-287422"/>
-    <hyperlink ref="E205" r:id="rId204" display="https://www.bookxcess.com/products/billie-joe-armstrong-pop-art-10x10-288003"/>
-    <hyperlink ref="E206" r:id="rId205" display="https://www.bookxcess.com/products/brandon-boyd-pop-art-10x10-287103"/>
-    <hyperlink ref="E207" r:id="rId206" display="https://www.bookxcess.com/products/david-guetta-pop-art-10x10"/>
-    <hyperlink ref="E208" r:id="rId207" display="https://www.bookxcess.com/products/dj-snake-pop-art-10x10-287614"/>
-    <hyperlink ref="E209" r:id="rId208" display="https://www.bookxcess.com/products/fred-durst-limp-bizkit-pop-art-10x10"/>
-    <hyperlink ref="E210" r:id="rId209" display="https://www.bookxcess.com/products/im-yoona-girls-generation-pop-art-10x10-286836"/>
-    <hyperlink ref="E211" r:id="rId210" display="https://www.bookxcess.com/products/justin-timberlake-the-most-boring-thing-pop-art-10x10-287575"/>
-    <hyperlink ref="E212" r:id="rId211" display="https://www.bookxcess.com/products/pharrel-williams-pop-art-10x10-286800"/>
-    <hyperlink ref="E213" r:id="rId212" display="https://www.bookxcess.com/products/pop-art-sam-smith-26-cm-x-26-cm"/>
-    <hyperlink ref="E214" r:id="rId213" display="https://www.bookxcess.com/products/t-ever-getting-older-pop-art-10x10-287711"/>
-    <hyperlink ref="E215" r:id="rId214" display="https://www.bookxcess.com/products/yoshiki-hayashi-x-japan-pop-art-10x10-287508"/>
-    <hyperlink ref="E216" r:id="rId215" display="https://www.sweelee.com.my/products/fender-amp-logo-patch"/>
-    <hyperlink ref="E217" r:id="rId216" display="https://www.sweelee.com.my/products/fender-bookmarks-set-of-3"/>
-    <hyperlink ref="E218" r:id="rId217" display="https://www.sweelee.com.my/products/fender-crossed-guitars-patch"/>
-    <hyperlink ref="E219" r:id="rId218" display="https://www.sweelee.com.my/products/prs-block-logo-clear-shot-glass"/>
-    <hyperlink ref="E220" r:id="rId219" display="https://www.sweelee.com.my/products/prs-camp-mug-maroon"/>
-    <hyperlink ref="E221" r:id="rId220" display="https://www.sweelee.com.my/products/prs-headstock-keychain"/>
-    <hyperlink ref="E222" r:id="rId221" display="https://tandangstore.com/products/-cave-in-heavy-pendulum-the-singles-live-at-bbc-s-maida-vale-studios-cassette-1"/>
-    <hyperlink ref="E223" r:id="rId222" display="https://tandangstore.com/products/pre-order-d-e-p-unapologetic-totebag-1-1-1"/>
-    <hyperlink ref="E224" r:id="rId223" display="https://tandangstore.com/products/-iron-fist-magazine-issue-24"/>
-    <hyperlink ref="E225" r:id="rId224" display="https://tandangstore.com/products/leo-nocentelli-another-side-cs"/>
-    <hyperlink ref="E226" r:id="rId225" display="https://tandangstore.com/products/shindig-issue-135-1"/>
-    <hyperlink ref="E227" r:id="rId226" display="https://tandangstore.com/products/shindig-issue-135"/>
-    <hyperlink ref="E228" r:id="rId227" display="https://tandangstore.com/products/-silampukau-sementara-ini-cassette"/>
-    <hyperlink ref="E229" r:id="rId228" display="https://xduniverse.com.my/products/2026-g-dragon-fam-meeting-fam-ily-family-fam-i-love-you-official-md-photocard-pack"/>
-    <hyperlink ref="E230" r:id="rId229" display="https://xduniverse.com.my/products/babymonster-world-tour-choom-in-seoul-official-md-trading-photocard"/>
-    <hyperlink ref="E231" r:id="rId230" display="https://xduniverse.com.my/products/bigbang-2026-2027-world-tour-xx-cosmos-official-merch-tour-reusable-bag"/>
-    <hyperlink ref="E232" r:id="rId231" display="https://xduniverse.com.my/products/cortis-tour-put-your-phone-down-in-japan-official-merch-mini-image-picket"/>
-    <hyperlink ref="E233" r:id="rId232" display="https://xduniverse.com.my/products/gd-g-dragon-zo-friends-lucky-shop-pop-up-zoa-random-figure-keyring"/>
-    <hyperlink ref="E234" r:id="rId233" display="https://xduniverse.com.my/products/itzy-the-4th-fan-meeting-md-on-air-trading-card-random-3-out-of-30"/>
-    <hyperlink ref="E235" r:id="rId234" display="https://xduniverse.com.my/products/iu-the-winning-photocard-set"/>
-    <hyperlink ref="E236" r:id="rId235" display="https://xduniverse.com.my/products/ive-world-tour-show-what-i-am-in-japan-official-md-random-trading-card"/>
-    <hyperlink ref="E237" r:id="rId236" display="https://xduniverse.com.my/products/le-sserafim-2025-tour-easy-crazy-hot-official-md-mini-photo-card"/>
-    <hyperlink ref="E238" r:id="rId237" display="https://xduniverse.com.my/products/line-friends-zeroni-monitor-figure"/>
-    <hyperlink ref="E239" r:id="rId238" display="https://xduniverse.com.my/products/nct-dream-9th-anniversary-md-lucky-card-set"/>
-    <hyperlink ref="E240" r:id="rId239" display="https://xduniverse.com.my/products/nct-wish-1st-concert-tour-into-the-wish-our-wish-encore-official-merch-wish-charm"/>
-    <hyperlink ref="E241" r:id="rId240" display="https://xduniverse.com.my/products/red-velvet-fan-con-a-day-in-red-velvet-official-md-random-trading-card"/>
-    <hyperlink ref="E242" r:id="rId241" display="https://xduniverse.com.my/products/seventeen-miniteen-4-0-official-merchandise-miniteen-photocard-holder"/>
-    <hyperlink ref="E243" r:id="rId242" display="https://xduniverse.com.my/products/seventeen-right-here-world-tour-in-japan-merch-acrylic-stand-joshua"/>
-    <hyperlink ref="E244" r:id="rId243" display="https://xduniverse.com.my/products/taeyang-quintessence-official-merch-random-trading-card"/>
-    <hyperlink ref="E245" r:id="rId244" display="https://xduniverse.com.my/products/txt-world-tour-act-tomorrow-in-japan-photocard"/>
-    <hyperlink ref="E246" r:id="rId245" display="https://xduniverse.com.my/products/wonpil-solo-concert-unpiltered-official-merch-4-cut-photo-set"/>
-    <hyperlink ref="E247" r:id="rId246" display="https://xduniverse.com.my/products/bptourmsh-blackpink-character-id-photo-holder"/>
-    <hyperlink ref="E248" r:id="rId247" display="https://xduniverse.com.my/products/aespa-week-make-it-lemonade-seoul-official-md-postcard-hologram-photo-card-set-wda-ver"/>
-    <hyperlink ref="E249" r:id="rId248" display="https://tandangstore.com/products/-mitski-be-the-cowboy-cassette-coming-soon--1"/>
+    <hyperlink ref="E197" r:id="rId196" display="https://www.bookxcess.com/products/bob-dylan-pop-art-10x10-286760"/>
+    <hyperlink ref="E198" r:id="rId197" display="https://xduniverse.com.my/products/aespa-fanlight-emblem"/>
+    <hyperlink ref="E199" r:id="rId198" display="https://www.sweelee.com.my/products/vinyl-styl-audio-cassette-head-cleaner-and-demagnetizer"/>
+    <hyperlink ref="E200" r:id="rId199" display="https://www.bookxcess.com/products/frank-sinatra-pop-art-10x10-287504"/>
+    <hyperlink ref="E201" r:id="rId200" display="https://www.bookxcess.com/products/dua-lipa_we-were-pop-art-10x10-287983"/>
+    <hyperlink ref="E202" r:id="rId201" display="https://www.bookxcess.com/products/paul-stanley-kiss-pop-art-10x10-287461"/>
+    <hyperlink ref="E203" r:id="rId202" display="https://xduniverse.com.my/products/twice-this-is-for-world-tour-in-japan-official-goods-random-trading-card"/>
+    <hyperlink ref="E204" r:id="rId203" display="https://xduniverse.com.my/products/stray-kids-6th-fanmeeting-stay-in-our-little-house-official-merch-special-trading-card"/>
+    <hyperlink ref="E205" r:id="rId204" display="https://tandangstore.com/products/-mitski-the-land-is-inhospitable-and-so-are-we-cassette-coming-soon-"/>
+    <hyperlink ref="E206" r:id="rId205" display="https://tandangstore.com/products/-new-arrival-godflesh-songs-of-love-and-hate-cassette-1"/>
+    <hyperlink ref="E207" r:id="rId206" display="https://www.bookxcess.com/products/armin-van-buuren-pop-art-10x10-287422"/>
+    <hyperlink ref="E208" r:id="rId207" display="https://www.bookxcess.com/products/billie-joe-armstrong-pop-art-10x10-288003"/>
+    <hyperlink ref="E209" r:id="rId208" display="https://www.bookxcess.com/products/brandon-boyd-pop-art-10x10-287103"/>
+    <hyperlink ref="E210" r:id="rId209" display="https://www.bookxcess.com/products/david-guetta-pop-art-10x10"/>
+    <hyperlink ref="E211" r:id="rId210" display="https://www.bookxcess.com/products/dj-snake-pop-art-10x10-287614"/>
+    <hyperlink ref="E212" r:id="rId211" display="https://www.bookxcess.com/products/fred-durst-limp-bizkit-pop-art-10x10"/>
+    <hyperlink ref="E213" r:id="rId212" display="https://www.bookxcess.com/products/im-yoona-girls-generation-pop-art-10x10-286836"/>
+    <hyperlink ref="E214" r:id="rId213" display="https://www.bookxcess.com/products/justin-timberlake-the-most-boring-thing-pop-art-10x10-287575"/>
+    <hyperlink ref="E215" r:id="rId214" display="https://www.bookxcess.com/products/pharrel-williams-pop-art-10x10-286800"/>
+    <hyperlink ref="E216" r:id="rId215" display="https://www.bookxcess.com/products/pop-art-sam-smith-26-cm-x-26-cm"/>
+    <hyperlink ref="E217" r:id="rId216" display="https://www.bookxcess.com/products/t-ever-getting-older-pop-art-10x10-287711"/>
+    <hyperlink ref="E218" r:id="rId217" display="https://www.bookxcess.com/products/yoshiki-hayashi-x-japan-pop-art-10x10-287508"/>
+    <hyperlink ref="E219" r:id="rId218" display="https://cottonon.com/MY/lisa-music-boxy-graphic-tee/2059306-158.html"/>
+    <hyperlink ref="E220" r:id="rId219" display="https://www.sweelee.com.my/products/fender-amp-logo-patch"/>
+    <hyperlink ref="E221" r:id="rId220" display="https://www.sweelee.com.my/products/fender-bookmarks-set-of-3"/>
+    <hyperlink ref="E222" r:id="rId221" display="https://www.sweelee.com.my/products/fender-crossed-guitars-patch"/>
+    <hyperlink ref="E223" r:id="rId222" display="https://www.sweelee.com.my/products/prs-block-logo-clear-shot-glass"/>
+    <hyperlink ref="E224" r:id="rId223" display="https://www.sweelee.com.my/products/prs-camp-mug-maroon"/>
+    <hyperlink ref="E225" r:id="rId224" display="https://www.sweelee.com.my/products/prs-headstock-keychain"/>
+    <hyperlink ref="E226" r:id="rId225" display="https://tandangstore.com/products/-cave-in-heavy-pendulum-the-singles-live-at-bbc-s-maida-vale-studios-cassette-1"/>
+    <hyperlink ref="E227" r:id="rId226" display="https://tandangstore.com/products/pre-order-d-e-p-unapologetic-totebag-1-1-1"/>
+    <hyperlink ref="E228" r:id="rId227" display="https://tandangstore.com/products/-iron-fist-magazine-issue-24"/>
+    <hyperlink ref="E229" r:id="rId228" display="https://tandangstore.com/products/leo-nocentelli-another-side-cs"/>
+    <hyperlink ref="E230" r:id="rId229" display="https://tandangstore.com/products/shindig-issue-135-1"/>
+    <hyperlink ref="E231" r:id="rId230" display="https://tandangstore.com/products/shindig-issue-135"/>
+    <hyperlink ref="E232" r:id="rId231" display="https://tandangstore.com/products/-silampukau-sementara-ini-cassette"/>
+    <hyperlink ref="E233" r:id="rId232" display="https://www.toysrus.com.my/jaki-pink-rose-music-box-10042194.html"/>
+    <hyperlink ref="E234" r:id="rId233" display="https://www.toysrus.com.my/kpop-demon-hunters-acrylic-board---huntr-x-10131256.html"/>
+    <hyperlink ref="E235" r:id="rId234" display="https://www.toysrus.com.my/kpop-demon-hunters-acrylic-standee---huntr-x-rumi-10131252.html"/>
+    <hyperlink ref="E236" r:id="rId235" display="https://www.toysrus.com.my/kpop-demon-hunters-flat-plush-keychain---huntrix-rumi-golden-version-10131258.html"/>
+    <hyperlink ref="E237" r:id="rId236" display="https://www.toysrus.com.my/kpop-demon-hunters-flat-plush-keychain---saja-boys-jinu-soda-pop-version-10131261.html"/>
+    <hyperlink ref="E238" r:id="rId237" display="https://xduniverse.com.my/products/2026-g-dragon-fam-meeting-fam-ily-family-fam-i-love-you-official-md-photocard-pack"/>
+    <hyperlink ref="E239" r:id="rId238" display="https://xduniverse.com.my/products/babymonster-world-tour-choom-in-seoul-official-md-trading-photocard"/>
+    <hyperlink ref="E240" r:id="rId239" display="https://xduniverse.com.my/products/bigbang-2026-2027-world-tour-xx-cosmos-official-merch-tour-reusable-bag"/>
+    <hyperlink ref="E241" r:id="rId240" display="https://xduniverse.com.my/products/cortis-tour-put-your-phone-down-in-japan-official-merch-mini-image-picket"/>
+    <hyperlink ref="E242" r:id="rId241" display="https://xduniverse.com.my/products/gd-g-dragon-zo-friends-lucky-shop-pop-up-zoa-random-figure-keyring"/>
+    <hyperlink ref="E243" r:id="rId242" display="https://xduniverse.com.my/products/itzy-the-4th-fan-meeting-md-on-air-trading-card-random-3-out-of-30"/>
+    <hyperlink ref="E244" r:id="rId243" display="https://xduniverse.com.my/products/iu-the-winning-photocard-set"/>
+    <hyperlink ref="E245" r:id="rId244" display="https://xduniverse.com.my/products/ive-world-tour-show-what-i-am-in-japan-official-md-random-trading-card"/>
+    <hyperlink ref="E246" r:id="rId245" display="https://xduniverse.com.my/products/le-sserafim-2025-tour-easy-crazy-hot-official-md-mini-photo-card"/>
+    <hyperlink ref="E247" r:id="rId246" display="https://xduniverse.com.my/products/line-friends-zeroni-monitor-figure"/>
+    <hyperlink ref="E248" r:id="rId247" display="https://xduniverse.com.my/products/nct-dream-9th-anniversary-md-lucky-card-set"/>
+    <hyperlink ref="E249" r:id="rId248" display="https://xduniverse.com.my/products/nct-wish-1st-concert-tour-into-the-wish-our-wish-encore-official-merch-wish-charm"/>
+    <hyperlink ref="E250" r:id="rId249" display="https://xduniverse.com.my/products/red-velvet-fan-con-a-day-in-red-velvet-official-md-random-trading-card"/>
+    <hyperlink ref="E251" r:id="rId250" display="https://xduniverse.com.my/products/seventeen-miniteen-4-0-official-merchandise-miniteen-photocard-holder"/>
+    <hyperlink ref="E252" r:id="rId251" display="https://xduniverse.com.my/products/seventeen-right-here-world-tour-in-japan-merch-acrylic-stand-joshua"/>
+    <hyperlink ref="E253" r:id="rId252" display="https://xduniverse.com.my/products/taeyang-quintessence-official-merch-random-trading-card"/>
+    <hyperlink ref="E254" r:id="rId253" display="https://xduniverse.com.my/products/txt-world-tour-act-tomorrow-in-japan-photocard"/>
+    <hyperlink ref="E255" r:id="rId254" display="https://xduniverse.com.my/products/wonpil-solo-concert-unpiltered-official-merch-4-cut-photo-set"/>
+    <hyperlink ref="E256" r:id="rId255" display="https://xduniverse.com.my/products/bptourmsh-blackpink-character-id-photo-holder"/>
+    <hyperlink ref="E257" r:id="rId256" display="https://xduniverse.com.my/products/aespa-week-make-it-lemonade-seoul-official-md-postcard-hologram-photo-card-set-wda-ver"/>
+    <hyperlink ref="E258" r:id="rId257" display="https://tandangstore.com/products/-mitski-be-the-cowboy-cassette-coming-soon--1"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -22179,7 +22578,7 @@
     <oddFooter/>
   </headerFooter>
   <tableParts>
-    <tablePart r:id="rId249"/>
+    <tablePart r:id="rId258"/>
   </tableParts>
 </worksheet>
 </file>